--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_CR_BRD-03_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_CR_BRD-03_Effort_Estimate_v1.0.xlsx
@@ -10,21 +10,30 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change requests" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Green items (OOTB)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR Effort" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beyond the BRD - OOTB" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration &amp; DM scope" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best practice (blue)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRD items to deliver" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$51</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Change requests'!$A$4:$V$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Change requests'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Green items (OOTB)'!$A$4:$G$12</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Green items (OOTB)'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Lists'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$Y$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'CR Effort'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$G$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Integration &amp; DM scope'!$A$4:$D$27</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Integration &amp; DM scope'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Best practice (blue)'!$A$4:$E$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Best practice (blue)'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BRD items to deliver'!$A$4:$D$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'BRD items to deliver'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Lists'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -60,12 +69,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="004B4B4B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
       <color rgb="004B4B4B"/>
       <sz val="10"/>
     </font>
@@ -121,6 +124,12 @@
       <b val="1"/>
       <color rgb="00004EA8"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="004B4B4B"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -187,25 +196,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -213,10 +222,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -232,23 +241,17 @@
     <xf numFmtId="4" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -368,7 +371,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>29</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -681,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E27"/>
+  <dimension ref="B4:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -715,7 +718,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>BRD-03 Product Maintenance – change requests of the FRS v1.3 (orange points) with their effort</t>
+          <t>BRD-03 Product Maintenance – points beyond the BRD of the FRS v1.3: change requests with their effort</t>
         </is>
       </c>
     </row>
@@ -843,60 +846,105 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Totals of the change requests of the FRS BRD-03 v1.3 (Annex Y)</t>
+          <t>Totals of the points beyond the BRD of the FRS v1.3 (Annex Y)</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>One row per orange point of the FRS v1.3 (Annex Y.2), effort in man-days by activity</t>
+          <t>One row per orange point of the FRS v1.3 (Annex Y.2), effort in man-days</t>
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>Green items (OOTB)</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Points of the FRS beyond the BRD that BIBS already provides (green in the FRS): no cost</t>
+          <t>Points beyond the BRD that the iNXT BrokerVerse OOTB platform provides (green): no cost</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="11" t="inlineStr">
         <is>
+          <t>Integration &amp; DM scope</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Covered by the Integration scope or the Data Migration scope (BRD-13): no CR cost here</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="inlineStr">
+        <is>
+          <t>Not in the BRD, the FRS or the OOTB platform: recommendations (Annex Y.6), not commitments</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>BRD requirements not fully met by the OOTB platform: in-scope delivery work for planning, not CRs</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="13" t="inlineStr">
+        <is>
           <t>Assumptions</t>
         </is>
       </c>
-      <c r="C24" s="12" t="inlineStr">
+      <c r="C27" s="14" t="inlineStr">
         <is>
           <t>Man-day, range and day rate used by the formulas</t>
         </is>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="D27" s="14" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="B27" s="15" t="inlineStr">
+    <row r="30" ht="26" customHeight="1">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -909,6 +957,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -921,7 +972,136 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="28" t="inlineStr">
+        <is>
+          <t>CR Effort: BRD relation</t>
+        </is>
+      </c>
+      <c r="B1" s="28" t="inlineStr">
+        <is>
+          <t>CR Effort: Complexity</t>
+        </is>
+      </c>
+      <c r="C1" s="28" t="inlineStr">
+        <is>
+          <t>CR Effort: Priority</t>
+        </is>
+      </c>
+      <c r="D1" s="28" t="inlineStr">
+        <is>
+          <t>Integration &amp; DM scope: Scope</t>
+        </is>
+      </c>
+      <c r="E1" s="28" t="inlineStr">
+        <is>
+          <t>Best practice (blue): Suggested priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Extends a BRD requirement</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Not in any BRD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Data Migration scope</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -931,7 +1111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1015,7 +1195,7 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B7" s="17" t="inlineStr">
@@ -1025,7 +1205,7 @@
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Change request number (also in the CR register and FRS Annex Y.2)</t>
+          <t>Change request (FRS Annex Y.2 and the CR register)</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr"/>
@@ -1033,7 +1213,7 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B8" s="18" t="inlineStr">
@@ -1051,7 +1231,7 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
@@ -1061,7 +1241,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>FRPM item or annex row</t>
+          <t>FR item or annex row</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr"/>
@@ -1069,7 +1249,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B10" s="18" t="inlineStr">
@@ -1087,7 +1267,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
@@ -1109,17 +1289,17 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Where the point comes from</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Where the point comes from</t>
+          <t>Document and section</t>
         </is>
       </c>
       <c r="D12" s="14" t="inlineStr"/>
@@ -1127,7 +1307,7 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
@@ -1145,17 +1325,17 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
-          <t>OOTB status (BIBS today)</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>What the platform offers today</t>
+          <t>Programme Feature List, column OOTB platform</t>
         </is>
       </c>
       <c r="D14" s="14" t="inlineStr"/>
@@ -1163,17 +1343,17 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>Estimate basis</t>
+          <t>OOTB evidence</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Size of the platform parts the change touches</t>
+          <t>Screen or function of brokerverse-platform, or 'not found'</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr"/>
@@ -1181,17 +1361,17 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>Analysis &amp; design (md)</t>
+          <t>Prepared for BIBS?</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Man-days</t>
+          <t>Yes / No / Partly, with what was done for BIBS in this project (the effort is given anyway: the value of the change request)</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr"/>
@@ -1199,17 +1379,17 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Backend (md)</t>
+          <t>Effort covers</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Man-days</t>
+          <t>For a Partial feature: the missing part only</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
@@ -1217,17 +1397,17 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>Frontend (md)</t>
+          <t>Estimate basis</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Man-days</t>
+          <t>Size of the platform parts the change touches</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr"/>
@@ -1235,12 +1415,12 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Testing (md)</t>
+          <t>Analysis &amp; design (md)</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -1253,12 +1433,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Documentation / UAT support (md)</t>
+          <t>Backend (md)</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -1271,17 +1451,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Total (md)</t>
+          <t>Frontend (md)</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Sum of the activities</t>
+          <t>Man-days</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr"/>
@@ -1289,17 +1469,17 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Low (-20%)</t>
+          <t>Testing (md)</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Total less the range</t>
+          <t>Man-days</t>
         </is>
       </c>
       <c r="D22" s="14" t="inlineStr"/>
@@ -1307,17 +1487,17 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>High (+20%)</t>
+          <t>Documentation / UAT support (md)</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Total plus the range</t>
+          <t>Man-days</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr"/>
@@ -1325,17 +1505,17 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>Cost (PHP)</t>
+          <t>Total (md)</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Total x day rate (Assumptions)</t>
+          <t>Sum of the activities</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr"/>
@@ -1343,61 +1523,53 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>Complexity</t>
+          <t>Low (-20%)</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Low / Medium / High</t>
-        </is>
-      </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Low, Medium, High</t>
-        </is>
-      </c>
+          <t>Total less the range</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>High (+20%)</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>High / Medium / Low</t>
-        </is>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>High, Medium, Low</t>
-        </is>
-      </c>
+          <t>Total plus the range</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>Dependencies</t>
+          <t>Cost (PHP)</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>What the change needs first</t>
+          <t>Total x day rate (Assumptions)</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr"/>
@@ -1405,53 +1577,61 @@
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>Complexity</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Scope assumed by the estimate</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr"/>
+          <t>Low / Medium / High</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>Low, Medium, High</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Green items (OOTB)</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Point number (FRS Annex Y.3)</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr"/>
+          <t>High / Medium / Low</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>High, Medium, Low</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
         <is>
-          <t>Green items (OOTB)</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>Dependencies</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>The point of the FRS</t>
+          <t>What the change needs first</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr"/>
@@ -1459,17 +1639,17 @@
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Green items (OOTB)</t>
+          <t>CR Effort</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>FRS reference</t>
+          <t>Assumptions</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>FRPM item</t>
+          <t>Scope assumed by the estimate</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr"/>
@@ -1477,17 +1657,17 @@
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
         <is>
-          <t>Green items (OOTB)</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>Where in BIBS</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Screen or function</t>
+          <t>Point (Annex Y.3)</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr"/>
@@ -1495,17 +1675,17 @@
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>Green items (OOTB)</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>BRD reference</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Not in the BRD</t>
+          <t>The point of the FRS</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr"/>
@@ -1513,17 +1693,17 @@
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
-          <t>Green items (OOTB)</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>OOTB status</t>
+          <t>FRS reference</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>FR item or annex</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr"/>
@@ -1531,23 +1711,319 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>Green items (OOTB)</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>Programme Feature List, column OOTB platform</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Beyond the BRD - OOTB</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>OOTB evidence</t>
+        </is>
+      </c>
+      <c r="C36" s="14" t="inlineStr">
+        <is>
+          <t>Screen or function of brokerverse-platform</t>
+        </is>
+      </c>
+      <c r="D36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Beyond the BRD - OOTB</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>BRD reference</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Not in the BRD</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Beyond the BRD - OOTB</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
           <t>Cost (md)</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>Zero: no development</t>
-        </is>
-      </c>
-      <c r="D35" s="12" t="inlineStr"/>
+      <c r="C38" s="14" t="inlineStr">
+        <is>
+          <t>Zero</t>
+        </is>
+      </c>
+      <c r="D38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Integration &amp; DM scope</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>Interface or data load</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Integration &amp; DM scope</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="C40" s="14" t="inlineStr">
+        <is>
+          <t>Integration or Data Migration</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr">
+        <is>
+          <t>Integration scope, Data Migration scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t>Integration &amp; DM scope</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="inlineStr">
+        <is>
+          <t>What is exchanged or loaded</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>Integration &amp; DM scope</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>Where in the FRS</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Annex</t>
+        </is>
+      </c>
+      <c r="D42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>Best practice</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C44" s="14" t="inlineStr">
+        <is>
+          <t>Insurance-broking practice</t>
+        </is>
+      </c>
+      <c r="D44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>Why it matters for a broker</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>Philippine market where relevant</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>Suggested priority</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>High / Medium / Low</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>High, Medium, Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>Indicative man-days</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>Indicative; not in the CR total</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>BRD ID</t>
+        </is>
+      </c>
+      <c r="C48" s="14" t="inlineStr">
+        <is>
+          <t>BRD requirement</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>BRD requirement</t>
+        </is>
+      </c>
+      <c r="C49" s="12" t="inlineStr">
+        <is>
+          <t>Text of the BRD</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
+          <t>Fit class of the fit-gap workbook</t>
+        </is>
+      </c>
+      <c r="D50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>What iNXT BrokerVerse offers out of the box</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="inlineStr">
+        <is>
+          <t>OOTB capability</t>
+        </is>
+      </c>
+      <c r="D51" s="12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D35"/>
+  <autoFilter ref="A4:D51"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -1568,10 +2044,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1585,7 +2061,7 @@
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Totals of the change requests of the FRS BRD-03 v1.3 (Annex Y)</t>
+          <t>Totals of the points beyond the BRD of the FRS v1.3 (Annex Y)</t>
         </is>
       </c>
     </row>
@@ -1608,7 +2084,7 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>Change requests (orange points of the FRS)</t>
+          <t>Points beyond the BRD available OOTB (green, no cost)</t>
         </is>
       </c>
       <c r="B5" s="12" t="n">
@@ -1618,7 +2094,7 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of which extend a BRD requirement</t>
+          <t>Change requests (orange)</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
@@ -1628,128 +2104,138 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  of which are not in any BRD</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>1</v>
+          <t>Man-days: Analysis &amp; design</t>
+        </is>
+      </c>
+      <c r="B7" s="12">
+        <f>SUM('CR Effort'!M5:M8)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Man-days: Analysis &amp; design</t>
+          <t>Man-days: Backend</t>
         </is>
       </c>
       <c r="B8" s="12">
-        <f>SUM('Change requests'!J5:J9)</f>
+        <f>SUM('CR Effort'!N5:N8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Man-days: Backend</t>
+          <t>Man-days: Frontend</t>
         </is>
       </c>
       <c r="B9" s="12">
-        <f>SUM('Change requests'!K5:K9)</f>
+        <f>SUM('CR Effort'!O5:O8)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Man-days: Frontend</t>
+          <t>Man-days: Testing</t>
         </is>
       </c>
       <c r="B10" s="12">
-        <f>SUM('Change requests'!L5:L9)</f>
+        <f>SUM('CR Effort'!P5:P8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>Man-days: Testing</t>
+          <t>Man-days: Documentation / UAT support</t>
         </is>
       </c>
       <c r="B11" s="12">
-        <f>SUM('Change requests'!M5:M9)</f>
+        <f>SUM('CR Effort'!Q5:Q8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>Man-days: Documentation / UAT support</t>
+          <t>Total change request man-days</t>
         </is>
       </c>
       <c r="B12" s="12">
-        <f>SUM('Change requests'!N5:N9)</f>
+        <f>SUM('CR Effort'!R5:R8)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Total man-days</t>
+          <t>Range low (-20%)</t>
         </is>
       </c>
       <c r="B13" s="12">
-        <f>SUM('Change requests'!O5:O9)</f>
+        <f>SUM('CR Effort'!S5:S8)</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Range low (-20%)</t>
+          <t>Range high (+20%)</t>
         </is>
       </c>
       <c r="B14" s="12">
-        <f>SUM('Change requests'!P5:P9)</f>
+        <f>SUM('CR Effort'!T5:T8)</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Range high (+20%)</t>
+          <t>Cost in PHP at the day rate of the Assumptions sheet</t>
         </is>
       </c>
       <c r="B15" s="12">
-        <f>SUM('Change requests'!Q5:Q9)</f>
+        <f>SUM('CR Effort'!U5:U8)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Cost in PHP at the day rate of the Assumptions sheet</t>
-        </is>
-      </c>
-      <c r="B16" s="12">
-        <f>SUM('Change requests'!R5:R9)</f>
-        <v/>
+          <t>Items covered by the Integration or Data Migration scope (no CR cost)</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Points beyond the BRD available in BIBS (green, no cost)</t>
+          <t>Best-practice recommendations (blue; indicative, not in the CR total)</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Best-practice indicative man-days (not in the CR total)</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:B17"/>
+  <autoFilter ref="A4:B18"/>
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:B517">
+  <conditionalFormatting sqref="A5:B518">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -1774,44 +2260,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:V10"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="34" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>Change requests</t>
+          <t>CR Effort</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>One row per orange point of the FRS v1.3 (Annex Y.2), effort in man-days by activity</t>
+          <t>One row per orange point of the FRS v1.3 (Annex Y.2), effort in man-days</t>
         </is>
       </c>
     </row>
@@ -1838,6 +2327,9 @@
       <c r="T3" s="20" t="n"/>
       <c r="U3" s="20" t="n"/>
       <c r="V3" s="20" t="n"/>
+      <c r="W3" s="20" t="n"/>
+      <c r="X3" s="20" t="n"/>
+      <c r="Y3" s="20" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
@@ -1867,7 +2359,7 @@
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Where the point comes from</t>
         </is>
       </c>
       <c r="G4" s="21" t="inlineStr">
@@ -1877,75 +2369,90 @@
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t>OOTB status (BIBS today)</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="I4" s="21" t="inlineStr">
         <is>
+          <t>OOTB evidence</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t>Prepared for BIBS?</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>Effort covers</t>
+        </is>
+      </c>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
           <t>Estimate basis</t>
         </is>
       </c>
-      <c r="J4" s="21" t="inlineStr">
+      <c r="M4" s="21" t="inlineStr">
         <is>
           <t>Analysis &amp; design (md)</t>
         </is>
       </c>
-      <c r="K4" s="21" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t>Backend (md)</t>
         </is>
       </c>
-      <c r="L4" s="21" t="inlineStr">
+      <c r="O4" s="21" t="inlineStr">
         <is>
           <t>Frontend (md)</t>
         </is>
       </c>
-      <c r="M4" s="21" t="inlineStr">
+      <c r="P4" s="21" t="inlineStr">
         <is>
           <t>Testing (md)</t>
         </is>
       </c>
-      <c r="N4" s="21" t="inlineStr">
+      <c r="Q4" s="21" t="inlineStr">
         <is>
           <t>Documentation / UAT support (md)</t>
         </is>
       </c>
-      <c r="O4" s="21" t="inlineStr">
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t>Total (md)</t>
         </is>
       </c>
-      <c r="P4" s="21" t="inlineStr">
+      <c r="S4" s="21" t="inlineStr">
         <is>
           <t>Low (-20%)</t>
         </is>
       </c>
-      <c r="Q4" s="21" t="inlineStr">
+      <c r="T4" s="21" t="inlineStr">
         <is>
           <t>High (+20%)</t>
         </is>
       </c>
-      <c r="R4" s="21" t="inlineStr">
+      <c r="U4" s="21" t="inlineStr">
         <is>
           <t>Cost (PHP)</t>
         </is>
       </c>
-      <c r="S4" s="21" t="inlineStr">
+      <c r="V4" s="21" t="inlineStr">
         <is>
           <t>Complexity</t>
         </is>
       </c>
-      <c r="T4" s="21" t="inlineStr">
+      <c r="W4" s="21" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="U4" s="21" t="inlineStr">
+      <c r="X4" s="21" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
-      <c r="V4" s="21" t="inlineStr">
+      <c r="Y4" s="21" t="inlineStr">
         <is>
           <t>Assumptions</t>
         </is>
@@ -1989,61 +2496,76 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Not available: the slip approval (negotiation service) sends the slip to the insurers but no notice to the preparer; the notice service of the platform is available and is reused.</t>
+          <t>PRD-019 Partial (no negotiation rounds or slip approval for a programme); WFL-010 Available (in-app notices)</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Negotiation service about 410 lines; stage notices about 70 lines used as the pattern.</t>
-        </is>
-      </c>
-      <c r="J5" s="22" t="n">
+          <t>not found: Packages has no slip approval and no notice to the preparer</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>Partial in BrokerVerse OOTB: notices are available, the package slip approval is not; effort for the notice of the slip decision only.</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>Negotiation service of BIBS about 410 lines; stage notices about 70 lines used as the pattern.</t>
+        </is>
+      </c>
+      <c r="M5" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="K5" s="22" t="n">
+      <c r="N5" s="22" t="n">
         <v>1.5</v>
       </c>
-      <c r="L5" s="22" t="n">
+      <c r="O5" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="22" t="n">
+      <c r="P5" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="N5" s="22" t="n">
+      <c r="Q5" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="O5" s="22">
-        <f>SUM(J5:N5)</f>
+      <c r="R5" s="22">
+        <f>SUM(M5:Q5)</f>
         <v/>
       </c>
-      <c r="P5" s="22">
-        <f>ROUND(O5*(1-Assumptions!$B$6),1)</f>
+      <c r="S5" s="22">
+        <f>ROUND(R5*(1-Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="Q5" s="22">
-        <f>ROUND(O5*(1+Assumptions!$B$6),1)</f>
+      <c r="T5" s="22">
+        <f>ROUND(R5*(1+Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="R5" s="23">
-        <f>O5*Assumptions!$B$7</f>
+      <c r="U5" s="23">
+        <f>R5*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="S5" s="12" t="inlineStr">
+      <c r="V5" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T5" s="24" t="inlineStr">
+      <c r="W5" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U5" s="12" t="inlineStr">
+      <c r="X5" s="12" t="inlineStr">
         <is>
           <t>Notice service and e-mail channel (Annex S, IN-08)</t>
         </is>
       </c>
-      <c r="V5" s="12" t="inlineStr">
+      <c r="Y5" s="12" t="inlineStr">
         <is>
           <t>Text NT-16 of Annex P approved as written; in-system notice with e-mail copy by preference.</t>
         </is>
@@ -2087,61 +2609,76 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>Partly available: each ManCom approver is told in the system with an e-mail copy, in one standard text; the two BDOI texts are to be added.</t>
+          <t>PRD-021 Not available (no committee step or hand-off)</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>ManCom routing about 270 lines; one notice method to extend.</t>
-        </is>
-      </c>
-      <c r="J6" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="22" t="n">
-        <v>0</v>
+          <t>not found: no ManCom or committee step</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>Partly: the ManCom routing with one standard notice and e-mail copy was prepared for BIBS in this project</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>Not available in BrokerVerse OOTB. The effort is for the two BDOI texts on top of the routing already delivered for BIBS.</t>
+        </is>
+      </c>
+      <c r="L6" s="12" t="inlineStr">
+        <is>
+          <t>ManCom routing of BIBS about 270 lines; one notice method to extend.</t>
+        </is>
       </c>
       <c r="M6" s="22" t="n">
         <v>0.5</v>
       </c>
       <c r="N6" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="22" t="n">
         <v>0.5</v>
       </c>
-      <c r="O6" s="22">
-        <f>SUM(J6:N6)</f>
+      <c r="Q6" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R6" s="22">
+        <f>SUM(M6:Q6)</f>
         <v/>
       </c>
-      <c r="P6" s="22">
-        <f>ROUND(O6*(1-Assumptions!$B$6),1)</f>
+      <c r="S6" s="22">
+        <f>ROUND(R6*(1-Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="Q6" s="22">
-        <f>ROUND(O6*(1+Assumptions!$B$6),1)</f>
+      <c r="T6" s="22">
+        <f>ROUND(R6*(1+Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="R6" s="23">
-        <f>O6*Assumptions!$B$7</f>
+      <c r="U6" s="23">
+        <f>R6*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="S6" s="12" t="inlineStr">
+      <c r="V6" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="T6" s="24" t="inlineStr">
+      <c r="W6" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="U6" s="12" t="inlineStr">
+      <c r="X6" s="12" t="inlineStr">
         <is>
           <t>E-mail channel of BDOI (Annex S, IN-08)</t>
         </is>
       </c>
-      <c r="V6" s="12" t="inlineStr">
+      <c r="Y6" s="12" t="inlineStr">
         <is>
           <t>Two texts; no attachment beyond the link to the request.</t>
         </is>
@@ -2155,93 +2692,108 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Old and new field values of product master changes in the audit log</t>
+          <t>Accessibility of the Product Maintenance screens (WCAG 2.2 level AA)</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>FRPM.021.01, FRPM.021.02; Annex M.5</t>
+          <t>Annex T, T-15</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>BRPM.024 (extends)</t>
+          <t>Not in BRD</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Extends a BRD requirement</t>
+          <t>Not in any BRD</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>FRS v1.2 Annex M.5 (observation: planned with the programme master data change log)</t>
+          <t>Programme register of non-functional requirements (NFR-ACC-01, NFR-ACC-02), proposed in FRS v1.2 Annex T</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>BRPM.024 asks for the audit trail of every action; the auditors also expect to see, for a changed master record, which field changed from which value to which value.</t>
+          <t>No BDOI BRD asks for an accessibility level; the programme register proposes WCAG 2.2 AA so that keyboard and screen-reader users can work in the module.</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>Partly available: every create, change and authorize of a product master is in the audit log with user and time; the field-by-field old and new values are kept today for package terms only.</t>
+          <t>NFR-021 Partial (contrast checked to WCAG AA in the theme; no accessibility statement or full WCAG audit)</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>15 catalogue services write the audit log; catalogue services about 35 files; record audit tab of the screens to show the two values.</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="n">
+          <t>Branding: contrast check only; no WCAG audit</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>Partly: the screens prepared for BIBS use the platform components; about 8 of 35 screen files carry accessibility labels</t>
+        </is>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>Partial in BrokerVerse OOTB; the effort covers the missing part only: the WCAG 2.2 AA check and fixes of the module screens.</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>Product Maintenance screens of BIBS: 35 files, about 3,800 lines.</t>
+        </is>
+      </c>
+      <c r="M7" s="22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N7" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="L7" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M7" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="N7" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O7" s="22">
-        <f>SUM(J7:N7)</f>
+      <c r="R7" s="22">
+        <f>SUM(M7:Q7)</f>
         <v/>
       </c>
-      <c r="P7" s="22">
-        <f>ROUND(O7*(1-Assumptions!$B$6),1)</f>
+      <c r="S7" s="22">
+        <f>ROUND(R7*(1-Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="Q7" s="22">
-        <f>ROUND(O7*(1+Assumptions!$B$6),1)</f>
+      <c r="T7" s="22">
+        <f>ROUND(R7*(1+Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="R7" s="23">
-        <f>O7*Assumptions!$B$7</f>
+      <c r="U7" s="23">
+        <f>R7*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="S7" s="12" t="inlineStr">
+      <c r="V7" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="T7" s="24" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="U7" s="12" t="inlineStr">
-        <is>
-          <t>Audit log of the platform (old and new value columns exist)</t>
-        </is>
-      </c>
-      <c r="V7" s="12" t="inlineStr">
-        <is>
-          <t>Product masters of the catalogue (products, coverages, clauses, field rules, incentive criteria, insurers, rates and taxes, sales organisation); values shown on the record audit tab.</t>
+      <c r="W7" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="X7" s="12" t="inlineStr">
+        <is>
+          <t>BDOI's decision on the accessibility level (Annex V, PQ18)</t>
+        </is>
+      </c>
+      <c r="Y7" s="12" t="inlineStr">
+        <is>
+          <t>Check and fixes on the 35 Product Maintenance screen files (about 3,800 lines) and the product master screens; no redesign.</t>
         </is>
       </c>
     </row>
@@ -2253,271 +2805,191 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Accessibility of the Product Maintenance screens (WCAG 2.2 level AA)</t>
+          <t>'Due soon' marker at 80% of the stage service level</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Annex T, T-15</t>
+          <t>FRPM.001.01</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Not in BRD</t>
+          <t>BRPM.021 (extends)</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Not in any BRD</t>
+          <t>Extends a BRD requirement</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Programme register of non-functional requirements (NFR-ACC-01, NFR-ACC-02), proposed in FRS v1.2 Annex T</t>
+          <t>FRS v1.1 FRPM.001.01 (amber from 80% of the stage service level)</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>No BDOI BRD asks for an accessibility level; the programme register proposes WCAG 2.2 AA so that keyboard and screen-reader users can work in the module.</t>
+          <t>BRPM.021 asks that each approval step is completed within the defined service level; an amber marker relative to each stage's own service level warns before the breach on short and long stages alike.</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Partly available: the screens use the platform components and are usable with the keyboard; no WCAG 2.2 AA conformance check has been made on the module (about 8 of 35 screen files carry accessibility labels).</t>
+          <t>WFL-007 Partial (deadlines and escalation for claims, complaints, leads and collections; no general turnaround engine)</t>
         </is>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>Product Maintenance screens: 35 files, about 3,800 lines.</t>
-        </is>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="22" t="n">
-        <v>6</v>
+          <t>not found for packages; Renewals use a fixed number of days</t>
+        </is>
+      </c>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>Partly: BIBS marks a package request 'due soon' 8 hours before its stage deadline and 'overdue' after it</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>Partial in BrokerVerse OOTB; the effort covers the missing part only: the marker at a percentage of each stage's service level.</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>Package query service of BIBS about 275 lines (fixed 8-hour window); stage age marker of the screens.</t>
+        </is>
       </c>
       <c r="M8" s="22" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="N8" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="O8" s="22">
-        <f>SUM(J8:N8)</f>
+      <c r="O8" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P8" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R8" s="22">
+        <f>SUM(M8:Q8)</f>
         <v/>
       </c>
-      <c r="P8" s="22">
-        <f>ROUND(O8*(1-Assumptions!$B$6),1)</f>
+      <c r="S8" s="22">
+        <f>ROUND(R8*(1-Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="Q8" s="22">
-        <f>ROUND(O8*(1+Assumptions!$B$6),1)</f>
+      <c r="T8" s="22">
+        <f>ROUND(R8*(1+Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="R8" s="23">
-        <f>O8*Assumptions!$B$7</f>
+      <c r="U8" s="23">
+        <f>R8*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="S8" s="12" t="inlineStr">
+      <c r="V8" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="W8" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="T8" s="24" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="U8" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's decision on the accessibility level (Annex V, PQ18)</t>
-        </is>
-      </c>
-      <c r="V8" s="12" t="inlineStr">
-        <is>
-          <t>Check and fixes on the 35 Product Maintenance screen files (about 3,800 lines) and the product master screens; no redesign.</t>
+      <c r="X8" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y8" s="12" t="inlineStr">
+        <is>
+          <t>The percentage is a parameter (default 80%) maintained by the System Administrator.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>CR-PM-105</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>'Due soon' marker at 80% of the stage service level</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>FRPM.001.01</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>BRPM.021 (extends)</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Extends a BRD requirement</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>FRS v1.1 FRPM.001.01 (amber from 80% of the stage service level)</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>BRPM.021 asks that each approval step is completed within the defined service level; an amber marker relative to each stage's own service level warns before the breach on short and long stages alike.</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>Partly available: a request is marked 'due soon' when it is due within 8 hours, whatever the service level of the stage; overdue (red) is available.</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>Package query service about 275 lines (fixed 8-hour window); stage age marker of the screens.</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M9" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" s="22" t="n">
-        <v>0.5</v>
+          <t>4 change requests</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="22">
+        <f>SUM(M5:M8)</f>
+        <v/>
+      </c>
+      <c r="N9" s="22">
+        <f>SUM(N5:N8)</f>
+        <v/>
       </c>
       <c r="O9" s="22">
-        <f>SUM(J9:N9)</f>
+        <f>SUM(O5:O8)</f>
         <v/>
       </c>
       <c r="P9" s="22">
-        <f>ROUND(O9*(1-Assumptions!$B$6),1)</f>
+        <f>SUM(P5:P8)</f>
         <v/>
       </c>
       <c r="Q9" s="22">
-        <f>ROUND(O9*(1+Assumptions!$B$6),1)</f>
+        <f>SUM(Q5:Q8)</f>
         <v/>
       </c>
-      <c r="R9" s="23">
-        <f>O9*Assumptions!$B$7</f>
+      <c r="R9" s="22">
+        <f>SUM(R5:R8)</f>
         <v/>
       </c>
-      <c r="S9" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="T9" s="24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="U9" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V9" s="12" t="inlineStr">
-        <is>
-          <t>The percentage is a parameter (default 80%) maintained by the System Administrator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>5 change requests</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="22">
-        <f>SUM(J5:J9)</f>
+      <c r="S9" s="22">
+        <f>SUM(S5:S8)</f>
         <v/>
       </c>
-      <c r="K10" s="22">
-        <f>SUM(K5:K9)</f>
+      <c r="T9" s="22">
+        <f>SUM(T5:T8)</f>
         <v/>
       </c>
-      <c r="L10" s="22">
-        <f>SUM(L5:L9)</f>
+      <c r="U9" s="23">
+        <f>SUM(U5:U8)</f>
         <v/>
       </c>
-      <c r="M10" s="22">
-        <f>SUM(M5:M9)</f>
-        <v/>
-      </c>
-      <c r="N10" s="22">
-        <f>SUM(N5:N9)</f>
-        <v/>
-      </c>
-      <c r="O10" s="22">
-        <f>SUM(O5:O9)</f>
-        <v/>
-      </c>
-      <c r="P10" s="22">
-        <f>SUM(P5:P9)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="22">
-        <f>SUM(Q5:Q9)</f>
-        <v/>
-      </c>
-      <c r="R10" s="23">
-        <f>SUM(R5:R9)</f>
-        <v/>
-      </c>
-      <c r="S10" s="12" t="n"/>
-      <c r="T10" s="25" t="n"/>
-      <c r="U10" s="12" t="n"/>
-      <c r="V10" s="12" t="n"/>
+      <c r="V9" s="12" t="n"/>
+      <c r="W9" s="12" t="n"/>
+      <c r="X9" s="12" t="n"/>
+      <c r="Y9" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:V10"/>
+  <autoFilter ref="A4:Y9"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A2:Y2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:V510">
+  <conditionalFormatting sqref="A5:Y509">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="E5:E510" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="BRD relation" error="Choose a value from the list (BRD relation)." type="list">
+    <dataValidation sqref="E5:E509" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="BRD relation" error="Choose a value from the list (BRD relation)." type="list">
       <formula1>'Lists'!$A$2:$A$3</formula1>
     </dataValidation>
-    <dataValidation sqref="S5:S510" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
+    <dataValidation sqref="V5:V509" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation sqref="T5:T510" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
+    <dataValidation sqref="W5:W509" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'Lists'!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -2541,29 +3013,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>Green items (OOTB)</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
-          <t>Points of the FRS beyond the BRD that BIBS already provides (green in the FRS): no cost</t>
+          <t>Points beyond the BRD that the iNXT BrokerVerse OOTB platform provides (green): no cost</t>
         </is>
       </c>
     </row>
@@ -2594,17 +3066,17 @@
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t>Where in BIBS</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
+          <t>OOTB evidence</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
           <t>BRD reference</t>
-        </is>
-      </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t>OOTB status</t>
         </is>
       </c>
       <c r="G4" s="21" t="inlineStr">
@@ -2621,27 +3093,27 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Excel export of the list behind each dashboard tile</t>
+          <t>TSU Workbench with the TSU queues by stage (team worklist)</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>FRPM.001.01</t>
+          <t>FRPM.002.01</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Product Maintenance dashboard, export buttons</t>
+          <t>WFL-005 Available</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
+          <t>My Work: personal and team worklists</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
           <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>Available in BIBS</t>
         </is>
       </c>
       <c r="G5" s="12" t="n">
@@ -2656,27 +3128,27 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Dashboard tiles of packages ending within 30, 60 and 90 days</t>
+          <t>Premium Calculator on the package rate scheme</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>FRPM.001.01</t>
+          <t>FRPM.002.01</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Dashboard stage tiles</t>
+          <t>PRD-005 Available</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
+          <t>Product Configurator &gt; Rating Engine: premium calculation</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
           <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>Available in BIBS</t>
         </is>
       </c>
       <c r="G6" s="12" t="n">
@@ -2691,27 +3163,27 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Dashboard tile of advisories drafted and not sent</t>
+          <t>Report exported to PDF, Excel and CSV, every run logged</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>FRPM.001.01</t>
+          <t>FRPM.019.01</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Dashboard stage tiles</t>
+          <t>RPT-011 Available; RPT-003 Partial (PDF, Excel and CSV available; Word and text exports, not asked here, are the missing part)</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
+          <t>Reports: exports and history of produced files</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
           <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Available in BIBS</t>
         </is>
       </c>
       <c r="G7" s="12" t="n">
@@ -2726,27 +3198,27 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Dashboard tile of the comparative outputs of the week</t>
+          <t>E-mail log with recipient, time, subject and attachment</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>FRPM.001.01</t>
+          <t>FRPM.021.01</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Dashboard stage tiles</t>
+          <t>WFL-011 Available</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
+          <t>E-mail outbox with the status of each e-mail</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
           <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>Available in BIBS</t>
         </is>
       </c>
       <c r="G8" s="12" t="n">
@@ -2761,144 +3233,39 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>TSU Workbench with the TSU queues by stage</t>
+          <t>Old and new field values of changed master records</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>FRPM.002.01</t>
+          <t>FRPM.021.01; Annex M.5</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>TSU Workbench screen</t>
+          <t>ADM-012 Available</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
+          <t>Audit trail: before and after values of every change</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
           <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Available in BIBS</t>
         </is>
       </c>
       <c r="G9" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>G-06</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Premium Calculator on the package rate scheme</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>FRPM.002.01</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Premium Calculator screen</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>Available in BIBS</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>G-07</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Renewal Request Report exported to PDF, Excel and CSV, every run logged</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>FRPM.019.01</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Report engine of the platform</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Available in BIBS</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>G-08</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>E-mail log with recipient, time, subject and attachment fingerprint</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>FRPM.021.01</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Message log of the platform</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>Available in BIBS</t>
-        </is>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:G12"/>
+  <autoFilter ref="A4:G9"/>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G512">
+  <conditionalFormatting sqref="A5:G509">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -2923,165 +3290,578 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="16" t="inlineStr">
         <is>
-          <t>Assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="26" t="inlineStr">
+          <t>Integration &amp; DM scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Covered by the Integration scope or the Data Migration scope (BRD-13): no CR cost here</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="20" t="n"/>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C3" s="26" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="27" t="inlineStr">
-        <is>
-          <t>Hours in a man-day</t>
-        </is>
-      </c>
-      <c r="B4" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="C4" s="27" t="inlineStr">
-        <is>
-          <t>One man-day (md) = 8 working hours</t>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Where in the FRS</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>PHP</t>
-        </is>
-      </c>
-      <c r="C5" s="27" t="inlineStr">
-        <is>
-          <t>Philippine peso</t>
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>IN-01 New Business (BRD-01)</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Products and their flags, the latest approved rate scheme of each package, rate exceptions, incentive indicators</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex S</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
-        <is>
-          <t>Estimate range (plus or minus)</t>
-        </is>
-      </c>
-      <c r="B6" s="28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C6" s="27" t="inlineStr">
-        <is>
-          <t>Each total is an estimate within plus or minus 20%</t>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>IN-02 New Business (BRD-01): client master</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Client look-up on client-specific package requests</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex S</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
-        <is>
-          <t>Day rate (PHP per man-day)</t>
-        </is>
-      </c>
-      <c r="B7" s="29" t="n"/>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>Enter the agreed day rate; the cost columns follow by formula</t>
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>IN-03 New Business (BRD-01): non-package requests</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Quotation requests, Quotation Slips, proposals and client responses (BDOI's FRPM.005 to FRPM.010)</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex S</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>Platform size</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="inlineStr">
-        <is>
-          <t>Effort estimated from the size of the platform parts each change touches (services, screens, notices) and a similar existing function</t>
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>IN-04 Operations (BRD-02)</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Package version for endorsement re-rating; incentive codes for commission</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex S</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>Activities</t>
-        </is>
-      </c>
-      <c r="B9" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" s="27" t="inlineStr">
-        <is>
-          <t>Analysis &amp; design, backend, frontend, testing, documentation / UAT support</t>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>IN-05 Renewal (BRD-06)</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Package version of the expiring account</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex S</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="27" t="inlineStr">
-        <is>
-          <t>BDOI decisions and inputs, BDOI testing time, data migration, infrastructure</t>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>IN-06 User Access Maintenance (BRD-11)</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Users, roles, sign-in through BDO sign-in (Entra ID)</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex S</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>Validity</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>30 days</t>
-        </is>
-      </c>
-      <c r="C11" s="27" t="inlineStr">
-        <is>
-          <t>Estimated again if the scope of a change request changes</t>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>IN-07 Data Migration (BRD-13)</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Go-live product masters, insurers, commission rates; package map of legacy packages</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex S</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>IN-08 E-mail channel of BDOI (Microsoft 365 or CCM)</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Quotation Slips, advisories, ManCom notices, password e-mails</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex S</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>IN-09 Insurers</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Protected Quotation Slips; replies received by e-mail and keyed in</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex S</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>IN-10 Document store (ECM)</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Package documents and attachments</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex S</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>IN-11 Other BDOI systems (to be named)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Integration scope</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Product master changes (package added, updated, deactivated or expired: product, version, effective date, request, status) in the file ProductMaster_yyyyMMddHHmmss.csv</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex S</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>U-01</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Data Migration scope</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Lists of values and parameters of Product Maintenance (request reasons, response outcomes, alert days, service levels, numbering prefixes)</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex U</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>U-02</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Data Migration scope</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Product lines, cover types / sub-lines and products (risk codes)</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex U</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>U-03</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Data Migration scope</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Coverages, perils and field rules per line</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex U</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>U-04</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Data Migration scope</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Clause library (warranties, clauses, exclusions, deductible wordings)</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex U</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>U-05</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Data Migration scope</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Rate tables and statutory charges</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex U</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>U-06</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Data Migration scope</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Insurers, insurer branches and placement e-mails</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex U</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>U-07</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Data Migration scope</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>Commission rates by insurer and product</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex U</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>U-08</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Data Migration scope</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Packages in force at go-live (set up through package requests, not loaded)</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex U</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>U-09</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Data Migration scope</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Package map (legacy package to BIBS package version)</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex U</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>U-10</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Data Migration scope</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Document templates of the package documents</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex U</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>U-11</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Data Migration scope</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>Incentive rules (CPC2 and others)</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex U</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>U-12</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Data Migration scope</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Users and roles of the module; ManCom approver list</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>FRS Annex U</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:D27"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:D527">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="B5:B527" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Scope" error="Choose a value from the list (Scope)." type="list">
+      <formula1>'Lists'!$D$2:$D$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -3102,78 +3882,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="30" t="inlineStr">
-        <is>
-          <t>Change requests: BRD relation</t>
-        </is>
-      </c>
-      <c r="B1" s="30" t="inlineStr">
-        <is>
-          <t>Change requests: Complexity</t>
-        </is>
-      </c>
-      <c r="C1" s="30" t="inlineStr">
-        <is>
-          <t>Change requests: Priority</t>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Extends a BRD requirement</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Not in the BRD, the FRS or the OOTB platform: recommendations (Annex Y.6), not commitments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="20" t="n"/>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Practice</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Why it matters for a broker</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>Suggested priority</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Indicative man-days</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>BP-PM-01</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Periodic package performance review: take-up, premium, claims experience and loss ratio per package, with a recorded decision to keep, redesign or retire it before renewal</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Packages sold through the bank stay fair value for clients and viable for insurers; Insurance Commission conduct expectations for products sold through banks</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>BP-PM-02</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Product disclosure sheet per package for the bank channel (key features, exclusions, insurer, BDOI's role as broker), produced from the released package version</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Bancassurance sales need clear pre-sale disclosure; one source avoids outdated brochures (Insurance Commission and BSP bancassurance rules)</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Not in any BRD</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="E6" s="12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>BP-PM-03</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Data-sharing record on client-specific packages: the basis for sharing with each insurer of the package and the client data sent in Quotation Slips</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Data Privacy Act: personal data shared with insurers needs a documented basis and only the minimum data</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
+      <c r="E7" s="12" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:E7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:E507">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="D5:D507" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Suggested priority" error="Choose a value from the list (Suggested priority)." type="list">
+      <formula1>'Lists'!$E$2:$E$4</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -3186,4 +4042,655 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>BRD requirements not fully met by the OOTB platform: in-scope delivery work for planning, not CRs</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="20" t="n"/>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>BRD ID</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>BRD requirement</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>What iNXT BrokerVerse offers out of the box</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>PMADD01</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>I want a standard reusable product structure hierarchy so that product data is consistent and scalable across packaged and non-packaged products.</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Configure</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>PRD-001 Single product catalogue keyed by BDOI risk code: Available – Line of business, product and cover masters with product templates per line; BDOI codes loaded as master data.
+PRD-002 Standard product hierarchy enforced complete: Partial – Line, product, template and Coverage Builder exist; no subtype level and no completeness rule on the hierarchy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>PMADD02</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>I want insurer-specific coverage, deductibles, and warranty mappings maintained without IT intervention so that insurer variability is supported in a controlled manner.</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Configure</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>PRD-014 Clause, warranty and exclusion library: Not available – Clauses and warranties are free text on offers and documents; no maintained library.
+PRD-015 Insurer-specific coverage, deductible and warranty mapping: Partial – Insurer rate tables per product (rate basis, minimum premium, deductible, commission) and market mapping terms; no coverage-level terms per insurer.
+PRD-016 Insurer panel per product: Available – Insurer panel per template; market restricted when the setting is on.
+QPL-016 Co-insurance with lead and shares: Available – Shares must total exactly 100% with one lead; taxes, payables and commission split per participant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>PMADD04</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>I want to have explicit exception states and iterative negotiation loop support so that non-linear insurer negotiations, revisions, and declines are handled as formal workflow outcomes rather than informal handling.</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Configure</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>PRD-019 Package negotiation rounds with insurers: Partial – Request for Quotation to several insurers with offers, declines and terms, set up for one client risk; no rounds or outcome states for a programme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>PMADD07</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>I want to define and maintain Incentive criteria based on the Maintained Products Matrix, so that incentives are accurately configured and applied only to eligible product combinations.</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Configure</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>PRD-026 Incentive criteria on the products matrix: Partial – Incentive programmes by target metric for account executives; no product-level eligibility criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>PMADD08</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>I must have a maintenance facility to define and update Incentives (i.e. CPC2) criteria based on the maintained products.</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Configure</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>PRD-026 Incentive criteria on the products matrix: Partial – Incentive programmes by target metric for account executives; no product-level eligibility criteria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.003</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>There must be a capability to capture, store, and validate all mandatory, critical and product-specific fields.</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Configure</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>PRD-003 Product-specific risk fields per line: Partial – Risk mappings with risk sections per product line; the quote wizard asks for the fields the rules test (require rule fields). No minimum-field matrix per product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.004</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>There must be a capability to apply validation rules based on product type.</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Configure</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>PRD-004 Configurable validation rules per product: Partial – Acceptance rules accept, refer, decline or load on risk fields; acceptance limits on sum insured and ages. No general data-validation rule set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.005</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>There must be a capability to use shared templates with dynamic fields for product-specific data.</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Configure</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>PRD-027 Document templates per product with merge fields: Available – Templates per product with merge fields and blocks, preview, printed on the letterhead; unknown merge fields refused.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.008</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Submit approved Package Request Form.</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Extend</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>PRD-018 Package request with multi-level approval: Not available – Products are created directly in the configurator; no request or approval chain.
+ADM-013 Document numbering formats: Available – 85 series with prefix, pattern, width, reset rule and start number; counters only move forward.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.011</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Facility to allow User to receive and view requests for product creation, amend, updating, or deletion based on client or business needs.</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Recommend change</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>PRD-018 Package request with multi-level approval: Not available – Products are created directly in the configurator; no request or approval chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.015</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Received product requirements from TSU. (i.e. computation and details that Marketing needed for their transactions). Product requirements and details from TSU are submitted via the system, triggering a ManCom review and signoff workflow. Only after ManCom’s in-system approval are requirements automatically forwarded to MBS for processing. MBS receives only validated, signed-off requirements and returns incomplete submissions. Marketing is notified by the system when the package is ready. While some manual steps (like physical signatures) may still occur, most information should flow through the system.</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Extend</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>PRD-005 Rating engine with factors, minimum premium and test calculator: Available – Multiplicative, discount and additive factors, minimum premium, illustration per template; the server re-prices every quotation.
+PRD-017 Package products with negotiated rates per insurer: Available – Bundles and insurer rate tables with minimum premium, deductible and commission per insurer and product.
+PRD-021 ManCom sign-off and hand-off to set-up: Not available – No requirements pack, committee step or hand-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.017</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>The system must enable the TSU Officer to monitor the expiry or anniversary date of each insurance package</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>Extend</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>PRD-023 Package expiry monitoring and renewal request: Partial – Template expiry dates and an expiring-templates list (warning period of 60 days); no renewal request.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.018</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Facility to allow User to generate Placement Update Reports (both for individual accounts and collectively for all accounts). This is to track and report the status of package creation, including key details such as but not limited to the following: account information, package status, expiry dates, terms, rates, and recent actions. Reports should support business monitoring, audit, and operational needs.</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Extend</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>PRD-024 Package status report and Product Maintenance dashboard: Partial – Template counts, categories, expiring templates and product analytics; no request status report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.019</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard for real-time tracking and reporting</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>Extend</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>PRD-024 Package status report and Product Maintenance dashboard: Partial – Template counts, categories, expiring templates and product analytics; no request status report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.020</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>Capability to check for document security (password protection/ encryption).</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Recommend change</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>QPL-031 Password-protected outbound documents: Not available – Documents are e-mailed as plain PDF attachments; signed download links expire after 30 minutes.
+WFL-020 Password-protected documents sent outside BDOI: Not available – Attachments are sent as plain PDF files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.022</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Notification and integration for seamless data flow.</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>Extend</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>PRD-029 Publish product master changes to other systems: Optional extra – an open interface available; no outbound product feed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.024</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>Ensure audit trail for all actions and changes.</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Extend</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>Audit history of changes per record.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:D21"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:D521">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Hours in a man-day</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>One man-day (md) = 8 working hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>Philippine peso</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Estimate range (plus or minus)</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>Each total is an estimate within plus or minus 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>DayRate (PHP per man-day)</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>Enter the agreed day rate; the cost columns follow by formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>OOTB baseline</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>brokerverse-platform</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>iNXT BrokerVerse OOTB platform (brokerverse-platform), with the programme Feature List (column OOTB platform) as a cross-check</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Platform size</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>Effort from the size of the platform parts each change touches and a similar existing function; for a Partial feature, the missing part only</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Not change requests</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>BRD requirements (in scope), Integration scope and Data Migration scope items, best-practice recommendations</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>BDOI decisions and inputs, BDOI testing time, infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Validity</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Estimated again if the scope of a change request changes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_CR_BRD-03_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_CR_BRD-03_Effort_Estimate_v1.0.xlsx
@@ -19,11 +19,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$52</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$Y$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$Y$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'CR Effort'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$G$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
@@ -31,7 +31,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Integration &amp; DM scope'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Best practice (blue)'!$A$4:$E$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Best practice (blue)'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BRD items to deliver'!$A$4:$D$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BRD items to deliver'!$A$4:$E$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'BRD items to deliver'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Lists'!$1:$1</definedName>
   </definedNames>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -1111,7 +1111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2022,8 +2022,26 @@
       </c>
       <c r="D51" s="12" t="inlineStr"/>
     </row>
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Planning man-days</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>For the points of BDOI's FRS covered by a BRD line</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:D51"/>
+  <autoFilter ref="A4:D52"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -2098,7 +2116,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2108,7 +2126,7 @@
         </is>
       </c>
       <c r="B7" s="12">
-        <f>SUM('CR Effort'!M5:M8)</f>
+        <f>SUM('CR Effort'!M5:M5)</f>
         <v/>
       </c>
     </row>
@@ -2119,7 +2137,7 @@
         </is>
       </c>
       <c r="B8" s="12">
-        <f>SUM('CR Effort'!N5:N8)</f>
+        <f>SUM('CR Effort'!N5:N5)</f>
         <v/>
       </c>
     </row>
@@ -2130,7 +2148,7 @@
         </is>
       </c>
       <c r="B9" s="12">
-        <f>SUM('CR Effort'!O5:O8)</f>
+        <f>SUM('CR Effort'!O5:O5)</f>
         <v/>
       </c>
     </row>
@@ -2141,7 +2159,7 @@
         </is>
       </c>
       <c r="B10" s="12">
-        <f>SUM('CR Effort'!P5:P8)</f>
+        <f>SUM('CR Effort'!P5:P5)</f>
         <v/>
       </c>
     </row>
@@ -2152,7 +2170,7 @@
         </is>
       </c>
       <c r="B11" s="12">
-        <f>SUM('CR Effort'!Q5:Q8)</f>
+        <f>SUM('CR Effort'!Q5:Q5)</f>
         <v/>
       </c>
     </row>
@@ -2163,7 +2181,7 @@
         </is>
       </c>
       <c r="B12" s="12">
-        <f>SUM('CR Effort'!R5:R8)</f>
+        <f>SUM('CR Effort'!R5:R5)</f>
         <v/>
       </c>
     </row>
@@ -2174,7 +2192,7 @@
         </is>
       </c>
       <c r="B13" s="12">
-        <f>SUM('CR Effort'!S5:S8)</f>
+        <f>SUM('CR Effort'!S5:S5)</f>
         <v/>
       </c>
     </row>
@@ -2185,7 +2203,7 @@
         </is>
       </c>
       <c r="B14" s="12">
-        <f>SUM('CR Effort'!T5:T8)</f>
+        <f>SUM('CR Effort'!T5:T5)</f>
         <v/>
       </c>
     </row>
@@ -2196,7 +2214,7 @@
         </is>
       </c>
       <c r="B15" s="12">
-        <f>SUM('CR Effort'!U5:U8)</f>
+        <f>SUM('CR Effort'!U5:U5)</f>
         <v/>
       </c>
     </row>
@@ -2260,7 +2278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2466,73 +2484,73 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Quotation Slip decision notice to the preparer</t>
+          <t>Accessibility of the Product Maintenance screens (WCAG 2.2 level AA)</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>FRPM.006.01, FRPM.012.01; Annex P NT-16</t>
+          <t>Annex T, T-15</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>BRPM.012 (extends)</t>
+          <t>Not in BRD</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Extends a BRD requirement</t>
+          <t>Not in any BRD</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>BDOI FRS v1.0 FRPM.006.01 and FRPM.012.01; FRS v1.2 Annex P (proposed text NT-16)</t>
+          <t>Programme register of non-functional requirements (NFR-ACC-01, NFR-ACC-02), proposed in FRS v1.2 Annex T</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>The TSU Officer who prepares a Quotation Slip learns of its approval or return only by opening the request; the notice lets the slip go to the insurers the same day.</t>
+          <t>No BDOI BRD asks for an accessibility level; the programme register proposes WCAG 2.2 AA so that keyboard and screen-reader users can work in the module.</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>PRD-019 Partial (no negotiation rounds or slip approval for a programme); WFL-010 Available (in-app notices)</t>
+          <t>NFR-021 Partial (contrast checked to WCAG AA in the theme; no accessibility statement or full WCAG audit)</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>not found: Packages has no slip approval and no notice to the preparer</t>
+          <t>Branding: contrast check only; no WCAG audit</t>
         </is>
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Partly: the screens prepared for BIBS use the platform components; about 8 of 35 screen files carry accessibility labels</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>Partial in BrokerVerse OOTB: notices are available, the package slip approval is not; effort for the notice of the slip decision only.</t>
+          <t>Partial in BrokerVerse OOTB; the effort covers the missing part only: the WCAG 2.2 AA check and fixes of the module screens.</t>
         </is>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>Negotiation service of BIBS about 410 lines; stage notices about 70 lines used as the pattern.</t>
+          <t>Product Maintenance screens of BIBS: 35 files, about 3,800 lines.</t>
         </is>
       </c>
       <c r="M5" s="22" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="N5" s="22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O5" s="22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P5" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="22" t="n">
         <v>1</v>
-      </c>
-      <c r="Q5" s="22" t="n">
-        <v>0.5</v>
       </c>
       <c r="R5" s="22">
         <f>SUM(M5:Q5)</f>
@@ -2552,444 +2570,105 @@
       </c>
       <c r="V5" s="12" t="inlineStr">
         <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="W5" s="12" t="inlineStr">
+        <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="W5" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
       <c r="X5" s="12" t="inlineStr">
         <is>
-          <t>Notice service and e-mail channel (Annex S, IN-08)</t>
+          <t>BDOI's decision on the accessibility level (Annex V, PQ18)</t>
         </is>
       </c>
       <c r="Y5" s="12" t="inlineStr">
         <is>
-          <t>Text NT-16 of Annex P approved as written; in-system notice with e-mail copy by preference.</t>
+          <t>Check and fixes on the 35 Product Maintenance screen files (about 3,800 lines) and the product master screens; no redesign.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>CR-PM-102</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>ManCom e-mails in BDOI's wording, with the President's text</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>FRPM.014.01; Annex P NT-13, NT-14</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>BRPM.015 (extends)</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Extends a BRD requirement</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>BDOI FRS v1.0 FRPM.014.01; FRS v1.2 Annex P (proposed texts NT-13, NT-14)</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's FRS asks for the ManCom approval e-mail in its own wording and a separate text when the request reaches the President.</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>PRD-021 Not available (no committee step or hand-off)</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>not found: no ManCom or committee step</t>
-        </is>
-      </c>
-      <c r="J6" s="12" t="inlineStr">
-        <is>
-          <t>Partly: the ManCom routing with one standard notice and e-mail copy was prepared for BIBS in this project</t>
-        </is>
-      </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>Not available in BrokerVerse OOTB. The effort is for the two BDOI texts on top of the routing already delivered for BIBS.</t>
-        </is>
-      </c>
-      <c r="L6" s="12" t="inlineStr">
-        <is>
-          <t>ManCom routing of BIBS about 270 lines; one notice method to extend.</t>
-        </is>
-      </c>
-      <c r="M6" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N6" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q6" s="22" t="n">
-        <v>0.5</v>
+          <t>1 change requests</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n"/>
+      <c r="D6" s="12" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="12" t="n"/>
+      <c r="G6" s="12" t="n"/>
+      <c r="H6" s="12" t="n"/>
+      <c r="I6" s="12" t="n"/>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
+      <c r="M6" s="22">
+        <f>SUM(M5:M5)</f>
+        <v/>
+      </c>
+      <c r="N6" s="22">
+        <f>SUM(N5:N5)</f>
+        <v/>
+      </c>
+      <c r="O6" s="22">
+        <f>SUM(O5:O5)</f>
+        <v/>
+      </c>
+      <c r="P6" s="22">
+        <f>SUM(P5:P5)</f>
+        <v/>
+      </c>
+      <c r="Q6" s="22">
+        <f>SUM(Q5:Q5)</f>
+        <v/>
       </c>
       <c r="R6" s="22">
-        <f>SUM(M6:Q6)</f>
+        <f>SUM(R5:R5)</f>
         <v/>
       </c>
       <c r="S6" s="22">
-        <f>ROUND(R6*(1-Assumptions!$B$6),1)</f>
+        <f>SUM(S5:S5)</f>
         <v/>
       </c>
       <c r="T6" s="22">
-        <f>ROUND(R6*(1+Assumptions!$B$6),1)</f>
+        <f>SUM(T5:T5)</f>
         <v/>
       </c>
       <c r="U6" s="23">
-        <f>R6*Assumptions!$B$7</f>
+        <f>SUM(U5:U5)</f>
         <v/>
       </c>
-      <c r="V6" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="W6" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="X6" s="12" t="inlineStr">
-        <is>
-          <t>E-mail channel of BDOI (Annex S, IN-08)</t>
-        </is>
-      </c>
-      <c r="Y6" s="12" t="inlineStr">
-        <is>
-          <t>Two texts; no attachment beyond the link to the request.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>CR-PM-103</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Accessibility of the Product Maintenance screens (WCAG 2.2 level AA)</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Annex T, T-15</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Not in any BRD</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Programme register of non-functional requirements (NFR-ACC-01, NFR-ACC-02), proposed in FRS v1.2 Annex T</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>No BDOI BRD asks for an accessibility level; the programme register proposes WCAG 2.2 AA so that keyboard and screen-reader users can work in the module.</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>NFR-021 Partial (contrast checked to WCAG AA in the theme; no accessibility statement or full WCAG audit)</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>Branding: contrast check only; no WCAG audit</t>
-        </is>
-      </c>
-      <c r="J7" s="12" t="inlineStr">
-        <is>
-          <t>Partly: the screens prepared for BIBS use the platform components; about 8 of 35 screen files carry accessibility labels</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>Partial in BrokerVerse OOTB; the effort covers the missing part only: the WCAG 2.2 AA check and fixes of the module screens.</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>Product Maintenance screens of BIBS: 35 files, about 3,800 lines.</t>
-        </is>
-      </c>
-      <c r="M7" s="22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="P7" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="22">
-        <f>SUM(M7:Q7)</f>
-        <v/>
-      </c>
-      <c r="S7" s="22">
-        <f>ROUND(R7*(1-Assumptions!$B$6),1)</f>
-        <v/>
-      </c>
-      <c r="T7" s="22">
-        <f>ROUND(R7*(1+Assumptions!$B$6),1)</f>
-        <v/>
-      </c>
-      <c r="U7" s="23">
-        <f>R7*Assumptions!$B$7</f>
-        <v/>
-      </c>
-      <c r="V7" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="W7" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="X7" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's decision on the accessibility level (Annex V, PQ18)</t>
-        </is>
-      </c>
-      <c r="Y7" s="12" t="inlineStr">
-        <is>
-          <t>Check and fixes on the 35 Product Maintenance screen files (about 3,800 lines) and the product master screens; no redesign.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>CR-PM-104</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>'Due soon' marker at 80% of the stage service level</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>FRPM.001.01</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>BRPM.021 (extends)</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Extends a BRD requirement</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>FRS v1.1 FRPM.001.01 (amber from 80% of the stage service level)</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>BRPM.021 asks that each approval step is completed within the defined service level; an amber marker relative to each stage's own service level warns before the breach on short and long stages alike.</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>WFL-007 Partial (deadlines and escalation for claims, complaints, leads and collections; no general turnaround engine)</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>not found for packages; Renewals use a fixed number of days</t>
-        </is>
-      </c>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>Partly: BIBS marks a package request 'due soon' 8 hours before its stage deadline and 'overdue' after it</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>Partial in BrokerVerse OOTB; the effort covers the missing part only: the marker at a percentage of each stage's service level.</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>Package query service of BIBS about 275 lines (fixed 8-hour window); stage age marker of the screens.</t>
-        </is>
-      </c>
-      <c r="M8" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P8" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R8" s="22">
-        <f>SUM(M8:Q8)</f>
-        <v/>
-      </c>
-      <c r="S8" s="22">
-        <f>ROUND(R8*(1-Assumptions!$B$6),1)</f>
-        <v/>
-      </c>
-      <c r="T8" s="22">
-        <f>ROUND(R8*(1+Assumptions!$B$6),1)</f>
-        <v/>
-      </c>
-      <c r="U8" s="23">
-        <f>R8*Assumptions!$B$7</f>
-        <v/>
-      </c>
-      <c r="V8" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="W8" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="X8" s="12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y8" s="12" t="inlineStr">
-        <is>
-          <t>The percentage is a parameter (default 80%) maintained by the System Administrator.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>4 change requests</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="22">
-        <f>SUM(M5:M8)</f>
-        <v/>
-      </c>
-      <c r="N9" s="22">
-        <f>SUM(N5:N8)</f>
-        <v/>
-      </c>
-      <c r="O9" s="22">
-        <f>SUM(O5:O8)</f>
-        <v/>
-      </c>
-      <c r="P9" s="22">
-        <f>SUM(P5:P8)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="22">
-        <f>SUM(Q5:Q8)</f>
-        <v/>
-      </c>
-      <c r="R9" s="22">
-        <f>SUM(R5:R8)</f>
-        <v/>
-      </c>
-      <c r="S9" s="22">
-        <f>SUM(S5:S8)</f>
-        <v/>
-      </c>
-      <c r="T9" s="22">
-        <f>SUM(T5:T8)</f>
-        <v/>
-      </c>
-      <c r="U9" s="23">
-        <f>SUM(U5:U8)</f>
-        <v/>
-      </c>
-      <c r="V9" s="12" t="n"/>
-      <c r="W9" s="12" t="n"/>
-      <c r="X9" s="12" t="n"/>
-      <c r="Y9" s="12" t="n"/>
+      <c r="V6" s="12" t="n"/>
+      <c r="W6" s="12" t="n"/>
+      <c r="X6" s="12" t="n"/>
+      <c r="Y6" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Y9"/>
+  <autoFilter ref="A4:Y6"/>
   <mergeCells count="1">
     <mergeCell ref="A2:Y2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:Y509">
+  <conditionalFormatting sqref="A5:Y506">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation sqref="E5:E509" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="BRD relation" error="Choose a value from the list (BRD relation)." type="list">
+    <dataValidation sqref="E5:E506" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="BRD relation" error="Choose a value from the list (BRD relation)." type="list">
       <formula1>'Lists'!$A$2:$A$3</formula1>
     </dataValidation>
-    <dataValidation sqref="V5:V509" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
+    <dataValidation sqref="V5:V506" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation sqref="W5:W509" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
+    <dataValidation sqref="W5:W506" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'Lists'!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -4050,13 +3729,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -4078,6 +3758,7 @@
       <c r="B3" s="20" t="n"/>
       <c r="C3" s="20" t="n"/>
       <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
@@ -4100,6 +3781,11 @@
           <t>What iNXT BrokerVerse offers out of the box</t>
         </is>
       </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Planning man-days</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
@@ -4123,6 +3809,7 @@
 PRD-002 Standard product hierarchy enforced complete: Partial – Line, product, template and Coverage Builder exist; no subtype level and no completeness rule on the hierarchy.</t>
         </is>
       </c>
+      <c r="E5" s="12" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
@@ -4148,6 +3835,7 @@
 QPL-016 Co-insurance with lead and shares: Available – Shares must total exactly 100% with one lead; taxes, payables and commission split per participant.</t>
         </is>
       </c>
+      <c r="E6" s="12" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
@@ -4170,6 +3858,7 @@
           <t>PRD-019 Package negotiation rounds with insurers: Partial – Request for Quotation to several insurers with offers, declines and terms, set up for one client risk; no rounds or outcome states for a programme.</t>
         </is>
       </c>
+      <c r="E7" s="12" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
@@ -4192,6 +3881,7 @@
           <t>PRD-026 Incentive criteria on the products matrix: Partial – Incentive programmes by target metric for account executives; no product-level eligibility criteria.</t>
         </is>
       </c>
+      <c r="E8" s="12" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
@@ -4214,6 +3904,7 @@
           <t>PRD-026 Incentive criteria on the products matrix: Partial – Incentive programmes by target metric for account executives; no product-level eligibility criteria.</t>
         </is>
       </c>
+      <c r="E9" s="12" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
@@ -4236,6 +3927,7 @@
           <t>PRD-003 Product-specific risk fields per line: Partial – Risk mappings with risk sections per product line; the quote wizard asks for the fields the rules test (require rule fields). No minimum-field matrix per product.</t>
         </is>
       </c>
+      <c r="E10" s="12" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
@@ -4258,6 +3950,7 @@
           <t>PRD-004 Configurable validation rules per product: Partial – Acceptance rules accept, refer, decline or load on risk fields; acceptance limits on sum insured and ages. No general data-validation rule set.</t>
         </is>
       </c>
+      <c r="E11" s="12" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
@@ -4280,6 +3973,7 @@
           <t>PRD-027 Document templates per product with merge fields: Available – Templates per product with merge fields and blocks, preview, printed on the letterhead; unknown merge fields refused.</t>
         </is>
       </c>
+      <c r="E12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
@@ -4303,6 +3997,7 @@
 ADM-013 Document numbering formats: Available – 85 series with prefix, pattern, width, reset rule and start number; counters only move forward.</t>
         </is>
       </c>
+      <c r="E13" s="12" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
@@ -4325,6 +4020,7 @@
           <t>PRD-018 Package request with multi-level approval: Not available – Products are created directly in the configurator; no request or approval chain.</t>
         </is>
       </c>
+      <c r="E14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
@@ -4349,6 +4045,7 @@
 PRD-021 ManCom sign-off and hand-off to set-up: Not available – No requirements pack, committee step or hand-off.</t>
         </is>
       </c>
+      <c r="E15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
@@ -4371,6 +4068,7 @@
           <t>PRD-023 Package expiry monitoring and renewal request: Partial – Template expiry dates and an expiring-templates list (warning period of 60 days); no renewal request.</t>
         </is>
       </c>
+      <c r="E16" s="12" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
@@ -4393,6 +4091,7 @@
           <t>PRD-024 Package status report and Product Maintenance dashboard: Partial – Template counts, categories, expiring templates and product analytics; no request status report.</t>
         </is>
       </c>
+      <c r="E17" s="12" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
@@ -4415,6 +4114,7 @@
           <t>PRD-024 Package status report and Product Maintenance dashboard: Partial – Template counts, categories, expiring templates and product analytics; no request status report.</t>
         </is>
       </c>
+      <c r="E18" s="12" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
@@ -4438,6 +4138,7 @@
 WFL-020 Password-protected documents sent outside BDOI: Not available – Attachments are sent as plain PDF files.</t>
         </is>
       </c>
+      <c r="E19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
@@ -4460,6 +4161,7 @@
           <t>PRD-029 Publish product master changes to other systems: Optional extra – an open interface available; no outbound product feed.</t>
         </is>
       </c>
+      <c r="E20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
@@ -4482,13 +4184,89 @@
           <t>Audit history of changes per record.</t>
         </is>
       </c>
+      <c r="E21" s="12" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>D-PM-01</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Quotation Slip decision notice to the preparer (FRPM.006.01, FRPM.012.01; Annex P NT-16). BRD line: BRPM.021 AC5: 'The system notifies users of pending validation or approval actions and tracks resolution within the SLA'; BRPM.012: 'Prepare and send quotation slip to Insurers'</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>BRD point to deliver</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>PRD-019 Partial (no negotiation rounds or slip approval for a programme); WFL-010 Available (in-app notices). Partial in BrokerVerse OOTB: notices are available, the package slip approval is not; effort for the notice of the slip decision only.</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>D-PM-02</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>ManCom e-mails in BDOI's wording, with the President's text (FRPM.014.01; Annex P NT-13, NT-14). BRD line: BRPM.015: 'a ManCom review and signoff workflow with audit logging'; BRPM.022: 'Notification and integration for seamless data flow'</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>BRD point to deliver</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>PRD-021 Not available (no committee step or hand-off). Not available in BrokerVerse OOTB. The effort is for the two BDOI texts on top of the routing already delivered for BIBS.</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>D-PM-03</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>'Due soon' marker at 80% of the stage service level (FRPM.001.01). BRD line: BRPM.021 ER3: 'Each approval step is completed by the designated authority ... within the defined SLA'; AC5 'tracks resolution within the SLA'</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>BRD point to deliver</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>WFL-007 Partial (deadlines and escalation for claims, complaints, leads and collections; no general turnaround engine). Partial in BrokerVerse OOTB; the planning effort covers the missing part only: the marker at a percentage of each stage's service level.</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>3.5</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D21"/>
+  <autoFilter ref="A4:E24"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:D521">
+  <conditionalFormatting sqref="A5:E524">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_CR_BRD-03_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_CR_BRD-03_Effort_Estimate_v1.0.xlsx
@@ -12,28 +12,31 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CR Effort" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Beyond the BRD - OOTB" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration &amp; DM scope" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best practice (blue)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRD items to deliver" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRD covered - OOTB" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration &amp; DM scope" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Best practice (blue)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRD items to deliver" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$59</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$Y$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'CR Effort'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$G$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Integration &amp; DM scope'!$A$4:$D$27</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Integration &amp; DM scope'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Best practice (blue)'!$A$4:$E$7</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Best practice (blue)'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'BRD items to deliver'!$A$4:$E$24</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'BRD items to deliver'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Lists'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'BRD covered - OOTB'!$A$4:$G$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'BRD covered - OOTB'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Integration &amp; DM scope'!$A$4:$D$27</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Integration &amp; DM scope'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Best practice (blue)'!$A$4:$E$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Best practice (blue)'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'BRD items to deliver'!$A$4:$E$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'BRD items to deliver'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Lists'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -371,7 +374,7 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="971550" cy="285750"/>
@@ -684,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E30"/>
+  <dimension ref="B4:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -850,7 +853,7 @@
         </is>
       </c>
       <c r="D21" s="14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -880,71 +883,86 @@
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Covered by the Integration scope or the Data Migration scope (BRD-13): no CR cost here</t>
+          <t>BRD requirements (black in the FRS, in scope) that the iNXT BrokerVerse OOTB platform provides: no change request, no effort</t>
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>Not in the BRD, the FRS or the OOTB platform: recommendations (Annex Y.6), not commitments</t>
+          <t>Covered by the Integration scope or the Data Migration scope (BRD-13): no CR cost here</t>
         </is>
       </c>
       <c r="D25" s="14" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>BRD requirements not fully met by the OOTB platform: in-scope delivery work for planning, not CRs</t>
+          <t>Not in the BRD, the FRS or the OOTB platform: recommendations (Annex Y.6), not commitments</t>
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="13" t="inlineStr">
         <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
+          <t>BRD requirements not fully met by the OOTB platform: in-scope delivery work for planning, not CRs</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="11" t="inlineStr">
+        <is>
           <t>Assumptions</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>Man-day, range and day rate used by the formulas</t>
         </is>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D28" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="B30" s="15" t="inlineStr">
+    <row r="31" ht="26" customHeight="1">
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>Prepared by iorta TechNXT for BDOI. Confidential – BDOI.</t>
         </is>
@@ -960,6 +978,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId9"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
@@ -972,11 +991,199 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Hours in a man-day</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>One man-day (md) = 8 working hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>PHP</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>Philippine peso</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Estimate range (plus or minus)</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>Each total is an estimate within plus or minus 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>DayRate (PHP per man-day)</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>Enter the agreed day rate; the cost columns follow by formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>OOTB baseline</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>brokerverse-platform</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>iNXT BrokerVerse OOTB platform (brokerverse-platform), with the programme Feature List (column OOTB platform) as a cross-check</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Platform size</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>Effort from the size of the platform parts each change touches and a similar existing function; for a Partial feature, the missing part only</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Not change requests</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>BRD requirements (in scope), Integration scope and Data Migration scope items, best-practice recommendations</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Excluded</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>BDOI decisions and inputs, BDOI testing time, infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Validity</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Estimated again if the scope of a change request changes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1111,7 +1318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1783,17 +1990,17 @@
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Interface or data load</t>
+          <t>Former green point</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -1801,39 +2008,35 @@
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Integration or Data Migration</t>
-        </is>
-      </c>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>Integration scope, Data Migration scope</t>
-        </is>
-      </c>
+          <t>The point of the FRS</t>
+        </is>
+      </c>
+      <c r="D40" s="14" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>What</t>
+          <t>FRS reference</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>What is exchanged or loaded</t>
+          <t>FR item or annex</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr"/>
@@ -1841,17 +2044,17 @@
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>Where in the FRS</t>
+          <t>BRD line</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Annex</t>
+          <t>The BRD line that asks for it (BRD, BRD-00 or programme-wide NFR)</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr"/>
@@ -1859,17 +2062,17 @@
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Best practice</t>
+          <t>Programme Feature List, column OOTB platform</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
@@ -1877,17 +2080,17 @@
     <row r="44">
       <c r="A44" s="14" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>Practice</t>
+          <t>OOTB evidence</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Insurance-broking practice</t>
+          <t>Screen or function of brokerverse-platform</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr"/>
@@ -1895,17 +2098,17 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>Why it matters for a broker</t>
+          <t>Effort (md)</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Philippine market where relevant</t>
+          <t>Zero: offered OOTB</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr"/>
@@ -1913,57 +2116,57 @@
     <row r="46">
       <c r="A46" s="14" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>Suggested priority</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>High / Medium / Low</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="inlineStr">
-        <is>
-          <t>High, Medium, Low</t>
-        </is>
-      </c>
+          <t>Interface or data load</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>Indicative man-days</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Indicative; not in the CR total</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr"/>
+          <t>Integration or Data Migration</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>Integration scope, Data Migration scope</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>BRD ID</t>
+          <t>What</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>BRD requirement</t>
+          <t>What is exchanged or loaded</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr"/>
@@ -1971,17 +2174,17 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>BRD requirement</t>
+          <t>Where in the FRS</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Text of the BRD</t>
+          <t>Annex</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr"/>
@@ -1989,17 +2192,17 @@
     <row r="50">
       <c r="A50" s="14" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Fit class of the fit-gap workbook</t>
+          <t>Best practice</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr"/>
@@ -2007,17 +2210,17 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>BRD items to deliver</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>What iNXT BrokerVerse offers out of the box</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>OOTB capability</t>
+          <t>Insurance-broking practice</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr"/>
@@ -2025,23 +2228,153 @@
     <row r="52">
       <c r="A52" s="14" t="inlineStr">
         <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Why it matters for a broker</t>
+        </is>
+      </c>
+      <c r="C52" s="14" t="inlineStr">
+        <is>
+          <t>Philippine market where relevant</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="inlineStr">
+        <is>
+          <t>Suggested priority</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>High / Medium / Low</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>High, Medium, Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>Best practice (blue)</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>Indicative man-days</t>
+        </is>
+      </c>
+      <c r="C54" s="14" t="inlineStr">
+        <is>
+          <t>Indicative; not in the CR total</t>
+        </is>
+      </c>
+      <c r="D54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
           <t>BRD items to deliver</t>
         </is>
       </c>
-      <c r="B52" s="18" t="inlineStr">
+      <c r="B55" s="17" t="inlineStr">
+        <is>
+          <t>BRD ID</t>
+        </is>
+      </c>
+      <c r="C55" s="12" t="inlineStr">
+        <is>
+          <t>BRD requirement</t>
+        </is>
+      </c>
+      <c r="D55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>BRD requirement</t>
+        </is>
+      </c>
+      <c r="C56" s="14" t="inlineStr">
+        <is>
+          <t>Text of the BRD</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>Fit</t>
+        </is>
+      </c>
+      <c r="C57" s="12" t="inlineStr">
+        <is>
+          <t>Fit class of the fit-gap workbook</t>
+        </is>
+      </c>
+      <c r="D57" s="12" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>What iNXT BrokerVerse offers out of the box</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
+          <t>OOTB capability</t>
+        </is>
+      </c>
+      <c r="D58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>BRD items to deliver</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>Planning man-days</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C59" s="12" t="inlineStr">
         <is>
           <t>For the points of BDOI's FRS covered by a BRD line</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr"/>
+      <c r="D59" s="12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:D52"/>
+  <autoFilter ref="A4:D59"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -2062,7 +2395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -2106,154 +2439,164 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>Change requests (orange)</t>
+          <t>BRD requirements offered OOTB (black, in scope, no effort)</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
+          <t>Change requests (orange)</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
           <t>Man-days: Analysis &amp; design</t>
         </is>
       </c>
-      <c r="B7" s="12">
+      <c r="B8" s="12">
         <f>SUM('CR Effort'!M5:M5)</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Man-days: Backend</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B9" s="12">
         <f>SUM('CR Effort'!N5:N5)</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Man-days: Frontend</t>
         </is>
       </c>
-      <c r="B9" s="12">
+      <c r="B10" s="12">
         <f>SUM('CR Effort'!O5:O5)</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>Man-days: Testing</t>
         </is>
       </c>
-      <c r="B10" s="12">
+      <c r="B11" s="12">
         <f>SUM('CR Effort'!P5:P5)</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>Man-days: Documentation / UAT support</t>
         </is>
       </c>
-      <c r="B11" s="12">
+      <c r="B12" s="12">
         <f>SUM('CR Effort'!Q5:Q5)</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Total change request man-days</t>
         </is>
       </c>
-      <c r="B12" s="12">
+      <c r="B13" s="12">
         <f>SUM('CR Effort'!R5:R5)</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Range low (-20%)</t>
         </is>
       </c>
-      <c r="B13" s="12">
+      <c r="B14" s="12">
         <f>SUM('CR Effort'!S5:S5)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>Range high (+20%)</t>
         </is>
       </c>
-      <c r="B14" s="12">
+      <c r="B15" s="12">
         <f>SUM('CR Effort'!T5:T5)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>Cost in PHP at the day rate of the Assumptions sheet</t>
         </is>
       </c>
-      <c r="B15" s="12">
+      <c r="B16" s="12">
         <f>SUM('CR Effort'!U5:U5)</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>Items covered by the Integration or Data Migration scope (no CR cost)</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>23</v>
-      </c>
-    </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Best-practice recommendations (blue; indicative, not in the CR total)</t>
+          <t>Items covered by the Integration or Data Migration scope (no CR cost)</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
+          <t>Best-practice recommendations (blue; indicative, not in the CR total)</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
           <t>Best-practice indicative man-days (not in the CR total)</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
+      <c r="B19" s="12" t="n">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:B18"/>
+  <autoFilter ref="A4:B19"/>
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:B518">
+  <conditionalFormatting sqref="A5:B519">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -2692,7 +3035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2767,12 +3110,12 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>G-01</t>
+          <t>G-02</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>TSU Workbench with the TSU queues by stage (team worklist)</t>
+          <t>Premium Calculator on the package rate scheme</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -2782,12 +3125,12 @@
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>WFL-005 Available</t>
+          <t>PRD-005 Available</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>My Work: personal and team worklists</t>
+          <t>Product Configurator &gt; Rating Engine: premium calculation</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -2799,152 +3142,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>G-02</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Premium Calculator on the package rate scheme</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>FRPM.002.01</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>PRD-005 Available</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Product Configurator &gt; Rating Engine: premium calculation</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>G-03</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Report exported to PDF, Excel and CSV, every run logged</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>FRPM.019.01</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>RPT-011 Available; RPT-003 Partial (PDF, Excel and CSV available; Word and text exports, not asked here, are the missing part)</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Reports: exports and history of produced files</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>G-04</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>E-mail log with recipient, time, subject and attachment</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>FRPM.021.01</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>WFL-011 Available</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>E-mail outbox with the status of each e-mail</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>G-05</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Old and new field values of changed master records</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>FRPM.021.01; Annex M.5</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>ADM-012 Available</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Audit trail: before and after values of every change</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Not in BRD</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:G9"/>
+  <autoFilter ref="A4:G5"/>
   <mergeCells count="1">
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:G509">
+  <conditionalFormatting sqref="A5:G505">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -2964,6 +3167,248 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>BRD covered - OOTB</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>BRD requirements (black in the FRS, in scope) that the iNXT BrokerVerse OOTB platform provides: no change request, no effort</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1">
+      <c r="A3" s="20" t="n"/>
+      <c r="B3" s="20" t="n"/>
+      <c r="C3" s="20" t="n"/>
+      <c r="D3" s="20" t="n"/>
+      <c r="E3" s="20" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="C4" s="21" t="inlineStr">
+        <is>
+          <t>FRS reference</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>BRD line</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>Feature List ID / OOTB status</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>OOTB evidence</t>
+        </is>
+      </c>
+      <c r="G4" s="21" t="inlineStr">
+        <is>
+          <t>Effort (md)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>G-01</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>TSU Workbench with the TSU queues by stage (team worklist)</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>FRPM.002.01</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.011 "Facility to allow User to receive and view requests for product creation, amend, updating, or deletion" ("The system displays all incoming requests with relevant details"); BRPM.019 "Dashboard for real-time tracking and reporting" ("Dashboard displays request status")</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>WFL-005 Available</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>My Work: personal and team worklists</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>G-03</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Report exported to PDF, Excel and CSV, every run logged</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>FRPM.019.01</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.018 "Reports are exportable in standard formats (PDF, Excel) for sharing or archiving"; "All report generation actions are logged for audit and traceability"</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>RPT-011 Available; RPT-003 Partial (PDF, Excel and CSV available; Word and text exports, not asked here, are the missing part)</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>Reports: exports and history of produced files</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>G-04</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>E-mail log with recipient, time, subject and attachment</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>FRPM.021.01</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.024 "Ensure audit trail for all actions and changes" ("System logs all actions (creation, edits, approvals, sharing) for traceability"); the advisory e-mails of the BRD are a sharing action</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>WFL-011 Available</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>E-mail outbox with the status of each e-mail</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>G-05</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Old and new field values of changed master records</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>FRPM.021.01; Annex M.5</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>BRPM.024 "Ensure audit trail for all actions and changes" ("Users can review a complete audit trail for any request or document"); programme NFR 4.01 "account changes" and 4.03 "Access and updates of customer records" (Collections, Claims, ReInsurance addenda)</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>ADM-012 Available</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Audit trail: before and after values of every change</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G8"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A5:G508">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3555,7 +4000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3723,7 +4168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4283,192 +4728,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>Assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="24" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B3" s="24" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="25" t="inlineStr">
-        <is>
-          <t>Hours in a man-day</t>
-        </is>
-      </c>
-      <c r="B4" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="C4" s="25" t="inlineStr">
-        <is>
-          <t>One man-day (md) = 8 working hours</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="25" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B5" s="25" t="inlineStr">
-        <is>
-          <t>PHP</t>
-        </is>
-      </c>
-      <c r="C5" s="25" t="inlineStr">
-        <is>
-          <t>Philippine peso</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>Estimate range (plus or minus)</t>
-        </is>
-      </c>
-      <c r="B6" s="26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C6" s="25" t="inlineStr">
-        <is>
-          <t>Each total is an estimate within plus or minus 20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="25" t="inlineStr">
-        <is>
-          <t>DayRate (PHP per man-day)</t>
-        </is>
-      </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="25" t="inlineStr">
-        <is>
-          <t>Enter the agreed day rate; the cost columns follow by formula</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="25" t="inlineStr">
-        <is>
-          <t>OOTB baseline</t>
-        </is>
-      </c>
-      <c r="B8" s="25" t="inlineStr">
-        <is>
-          <t>brokerverse-platform</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="inlineStr">
-        <is>
-          <t>iNXT BrokerVerse OOTB platform (brokerverse-platform), with the programme Feature List (column OOTB platform) as a cross-check</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-      <c r="B9" s="25" t="inlineStr">
-        <is>
-          <t>Platform size</t>
-        </is>
-      </c>
-      <c r="C9" s="25" t="inlineStr">
-        <is>
-          <t>Effort from the size of the platform parts each change touches and a similar existing function; for a Partial feature, the missing part only</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>Not change requests</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="25" t="inlineStr">
-        <is>
-          <t>BRD requirements (in scope), Integration scope and Data Migration scope items, best-practice recommendations</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>Excluded</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="25" t="inlineStr">
-        <is>
-          <t>BDOI decisions and inputs, BDOI testing time, infrastructure</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="25" t="inlineStr">
-        <is>
-          <t>Validity</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>30 days</t>
-        </is>
-      </c>
-      <c r="C12" s="25" t="inlineStr">
-        <is>
-          <t>Estimated again if the scope of a change request changes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_CR_BRD-03_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_CR_BRD-03_Effort_Estimate_v1.0.xlsx
@@ -20,11 +20,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Summary'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$Y$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CR Effort'!$A$4:$X$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'CR Effort'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Beyond the BRD - OOTB'!$A$4:$G$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Beyond the BRD - OOTB'!$4:$4</definedName>
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -697,13 +697,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -732,6 +735,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -804,6 +808,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -961,6 +966,8 @@
         <v>0</v>
       </c>
     </row>
+    <row r="29"/>
+    <row r="30"/>
     <row r="31" ht="26" customHeight="1">
       <c r="B31" s="15" t="inlineStr">
         <is>
@@ -1016,6 +1023,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="24" t="inlineStr">
         <is>
@@ -1318,7 +1326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1341,6 +1349,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1573,12 +1582,12 @@
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
-          <t>Prepared for BIBS?</t>
+          <t>Effort covers</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Yes / No / Partly, with what was done for BIBS in this project (the effort is given anyway: the value of the change request)</t>
+          <t>For a Partial feature: the missing part only</t>
         </is>
       </c>
       <c r="D16" s="14" t="inlineStr"/>
@@ -1591,12 +1600,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Effort covers</t>
+          <t>Estimate basis</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>For a Partial feature: the missing part only</t>
+          <t>Size of the platform parts the change touches</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
@@ -1609,12 +1618,12 @@
       </c>
       <c r="B18" s="18" t="inlineStr">
         <is>
-          <t>Estimate basis</t>
+          <t>Analysis &amp; design (md)</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Size of the platform parts the change touches</t>
+          <t>Man-days</t>
         </is>
       </c>
       <c r="D18" s="14" t="inlineStr"/>
@@ -1627,7 +1636,7 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>Analysis &amp; design (md)</t>
+          <t>Backend (md)</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -1645,7 +1654,7 @@
       </c>
       <c r="B20" s="18" t="inlineStr">
         <is>
-          <t>Backend (md)</t>
+          <t>Frontend (md)</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -1663,7 +1672,7 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>Frontend (md)</t>
+          <t>Testing (md)</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
@@ -1681,7 +1690,7 @@
       </c>
       <c r="B22" s="18" t="inlineStr">
         <is>
-          <t>Testing (md)</t>
+          <t>Documentation / UAT support (md)</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -1699,12 +1708,12 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Documentation / UAT support (md)</t>
+          <t>Total (md)</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Man-days</t>
+          <t>Sum of the activities</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr"/>
@@ -1717,12 +1726,12 @@
       </c>
       <c r="B24" s="18" t="inlineStr">
         <is>
-          <t>Total (md)</t>
+          <t>Low (-20%)</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Sum of the activities</t>
+          <t>Total less the range</t>
         </is>
       </c>
       <c r="D24" s="14" t="inlineStr"/>
@@ -1735,12 +1744,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>Low (-20%)</t>
+          <t>High (+20%)</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Total less the range</t>
+          <t>Total plus the range</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr"/>
@@ -1753,12 +1762,12 @@
       </c>
       <c r="B26" s="18" t="inlineStr">
         <is>
-          <t>High (+20%)</t>
+          <t>Cost (PHP)</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Total plus the range</t>
+          <t>Total x day rate (Assumptions)</t>
         </is>
       </c>
       <c r="D26" s="14" t="inlineStr"/>
@@ -1771,15 +1780,19 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>Cost (PHP)</t>
+          <t>Complexity</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Total x day rate (Assumptions)</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr"/>
+          <t>Low / Medium / High</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Low, Medium, High</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
@@ -1789,17 +1802,17 @@
       </c>
       <c r="B28" s="18" t="inlineStr">
         <is>
-          <t>Complexity</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>Low / Medium / High</t>
+          <t>High / Medium / Low</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>Low, Medium, High</t>
+          <t>High, Medium, Low</t>
         </is>
       </c>
     </row>
@@ -1811,19 +1824,15 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Dependencies</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>High / Medium / Low</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>High, Medium, Low</t>
-        </is>
-      </c>
+          <t>What the change needs first</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -1833,12 +1842,12 @@
       </c>
       <c r="B30" s="18" t="inlineStr">
         <is>
-          <t>Dependencies</t>
+          <t>Assumptions</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>What the change needs first</t>
+          <t>Scope assumed by the estimate</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr"/>
@@ -1846,17 +1855,17 @@
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>CR Effort</t>
+          <t>Beyond the BRD - OOTB</t>
         </is>
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>Assumptions</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Scope assumed by the estimate</t>
+          <t>Point (Annex Y.3)</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr"/>
@@ -1869,12 +1878,12 @@
       </c>
       <c r="B32" s="18" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Point (Annex Y.3)</t>
+          <t>The point of the FRS</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr"/>
@@ -1887,12 +1896,12 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>FRS reference</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>The point of the FRS</t>
+          <t>FR item or annex</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr"/>
@@ -1905,12 +1914,12 @@
       </c>
       <c r="B34" s="18" t="inlineStr">
         <is>
-          <t>FRS reference</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>FR item or annex</t>
+          <t>Programme Feature List, column OOTB platform</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr"/>
@@ -1923,12 +1932,12 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>Feature List ID / OOTB status</t>
+          <t>OOTB evidence</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Programme Feature List, column OOTB platform</t>
+          <t>Screen or function of brokerverse-platform</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr"/>
@@ -1941,12 +1950,12 @@
       </c>
       <c r="B36" s="18" t="inlineStr">
         <is>
-          <t>OOTB evidence</t>
+          <t>BRD reference</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>Screen or function of brokerverse-platform</t>
+          <t>Not in the BRD</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr"/>
@@ -1959,12 +1968,12 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>BRD reference</t>
+          <t>Cost (md)</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Not in the BRD</t>
+          <t>Zero</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr"/>
@@ -1972,17 +1981,17 @@
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
-          <t>Beyond the BRD - OOTB</t>
+          <t>BRD covered - OOTB</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
         <is>
-          <t>Cost (md)</t>
+          <t>No.</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Zero</t>
+          <t>Former green point</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr"/>
@@ -1995,12 +2004,12 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>No.</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Former green point</t>
+          <t>The point of the FRS</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -2013,12 +2022,12 @@
       </c>
       <c r="B40" s="18" t="inlineStr">
         <is>
-          <t>Point</t>
+          <t>FRS reference</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>The point of the FRS</t>
+          <t>FR item or annex</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr"/>
@@ -2031,12 +2040,12 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>FRS reference</t>
+          <t>BRD line</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>FR item or annex</t>
+          <t>The BRD line that asks for it (BRD, BRD-00 or programme-wide NFR)</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr"/>
@@ -2049,12 +2058,12 @@
       </c>
       <c r="B42" s="18" t="inlineStr">
         <is>
-          <t>BRD line</t>
+          <t>Feature List ID / OOTB status</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>The BRD line that asks for it (BRD, BRD-00 or programme-wide NFR)</t>
+          <t>Programme Feature List, column OOTB platform</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr"/>
@@ -2067,12 +2076,12 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>Feature List ID / OOTB status</t>
+          <t>OOTB evidence</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Programme Feature List, column OOTB platform</t>
+          <t>Screen or function of brokerverse-platform</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr"/>
@@ -2085,12 +2094,12 @@
       </c>
       <c r="B44" s="18" t="inlineStr">
         <is>
-          <t>OOTB evidence</t>
+          <t>Effort (md)</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Screen or function of brokerverse-platform</t>
+          <t>Zero: offered OOTB</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr"/>
@@ -2098,17 +2107,17 @@
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>BRD covered - OOTB</t>
+          <t>Integration &amp; DM scope</t>
         </is>
       </c>
       <c r="B45" s="17" t="inlineStr">
         <is>
-          <t>Effort (md)</t>
+          <t>Item</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Zero: offered OOTB</t>
+          <t>Interface or data load</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr"/>
@@ -2121,15 +2130,19 @@
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Scope</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Interface or data load</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="inlineStr"/>
+          <t>Integration or Data Migration</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>Integration scope, Data Migration scope</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
@@ -2139,19 +2152,15 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>Scope</t>
+          <t>What</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Integration or Data Migration</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>Integration scope, Data Migration scope</t>
-        </is>
-      </c>
+          <t>What is exchanged or loaded</t>
+        </is>
+      </c>
+      <c r="D47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="14" t="inlineStr">
@@ -2161,12 +2170,12 @@
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>What</t>
+          <t>Where in the FRS</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>What is exchanged or loaded</t>
+          <t>Annex</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr"/>
@@ -2174,17 +2183,17 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>Integration &amp; DM scope</t>
+          <t>Best practice (blue)</t>
         </is>
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>Where in the FRS</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Annex</t>
+          <t>Best practice</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr"/>
@@ -2197,12 +2206,12 @@
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Practice</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Best practice</t>
+          <t>Insurance-broking practice</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr"/>
@@ -2215,12 +2224,12 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>Practice</t>
+          <t>Why it matters for a broker</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Insurance-broking practice</t>
+          <t>Philippine market where relevant</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr"/>
@@ -2233,15 +2242,19 @@
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>Why it matters for a broker</t>
+          <t>Suggested priority</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Philippine market where relevant</t>
-        </is>
-      </c>
-      <c r="D52" s="14" t="inlineStr"/>
+          <t>High / Medium / Low</t>
+        </is>
+      </c>
+      <c r="D52" s="14" t="inlineStr">
+        <is>
+          <t>High, Medium, Low</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
@@ -2251,34 +2264,30 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>Suggested priority</t>
+          <t>Indicative man-days</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>High / Medium / Low</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>High, Medium, Low</t>
-        </is>
-      </c>
+          <t>Indicative; not in the CR total</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="14" t="inlineStr">
         <is>
-          <t>Best practice (blue)</t>
+          <t>BRD items to deliver</t>
         </is>
       </c>
       <c r="B54" s="18" t="inlineStr">
         <is>
-          <t>Indicative man-days</t>
+          <t>BRD ID</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Indicative; not in the CR total</t>
+          <t>BRD requirement</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr"/>
@@ -2291,12 +2300,12 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>BRD ID</t>
+          <t>BRD requirement</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>BRD requirement</t>
+          <t>Text of the BRD</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr"/>
@@ -2309,12 +2318,12 @@
       </c>
       <c r="B56" s="18" t="inlineStr">
         <is>
-          <t>BRD requirement</t>
+          <t>Fit</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Text of the BRD</t>
+          <t>Fit class of the fit-gap workbook</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr"/>
@@ -2327,12 +2336,12 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>Fit</t>
+          <t>What iNXT BrokerVerse offers out of the box</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Fit class of the fit-gap workbook</t>
+          <t>OOTB capability</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr"/>
@@ -2345,36 +2354,18 @@
       </c>
       <c r="B58" s="18" t="inlineStr">
         <is>
-          <t>What iNXT BrokerVerse offers out of the box</t>
+          <t>Planning man-days</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
         <is>
-          <t>OOTB capability</t>
+          <t>For the points of BDOI's FRS covered by a BRD line</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr"/>
     </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>BRD items to deliver</t>
-        </is>
-      </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>Planning man-days</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>For the points of BDOI's FRS covered by a BRD line</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:D59"/>
+  <autoFilter ref="A4:D58"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
@@ -2469,87 +2460,87 @@
         </is>
       </c>
       <c r="B8" s="12">
+        <f>SUM('CR Effort'!L5:L5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Man-days: Backend</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
         <f>SUM('CR Effort'!M5:M5)</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Man-days: Backend</t>
-        </is>
-      </c>
-      <c r="B9" s="12">
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Man-days: Frontend</t>
+        </is>
+      </c>
+      <c r="B10" s="12">
         <f>SUM('CR Effort'!N5:N5)</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Man-days: Frontend</t>
-        </is>
-      </c>
-      <c r="B10" s="12">
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Man-days: Testing</t>
+        </is>
+      </c>
+      <c r="B11" s="12">
         <f>SUM('CR Effort'!O5:O5)</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Man-days: Testing</t>
-        </is>
-      </c>
-      <c r="B11" s="12">
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Man-days: Documentation / UAT support</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
         <f>SUM('CR Effort'!P5:P5)</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Man-days: Documentation / UAT support</t>
-        </is>
-      </c>
-      <c r="B12" s="12">
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Total change request man-days</t>
+        </is>
+      </c>
+      <c r="B13" s="12">
         <f>SUM('CR Effort'!Q5:Q5)</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Total change request man-days</t>
-        </is>
-      </c>
-      <c r="B13" s="12">
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Range low (-20%)</t>
+        </is>
+      </c>
+      <c r="B14" s="12">
         <f>SUM('CR Effort'!R5:R5)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Range low (-20%)</t>
-        </is>
-      </c>
-      <c r="B14" s="12">
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Range high (+20%)</t>
+        </is>
+      </c>
+      <c r="B15" s="12">
         <f>SUM('CR Effort'!S5:S5)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Range high (+20%)</t>
-        </is>
-      </c>
-      <c r="B15" s="12">
-        <f>SUM('CR Effort'!T5:T5)</f>
-        <v/>
-      </c>
-    </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
@@ -2557,7 +2548,7 @@
         </is>
       </c>
       <c r="B16" s="12">
-        <f>SUM('CR Effort'!U5:U5)</f>
+        <f>SUM('CR Effort'!T5:T5)</f>
         <v/>
       </c>
     </row>
@@ -2621,7 +2612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2633,22 +2624,21 @@
     <col width="38" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
     <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
-    <col width="26" customWidth="1" min="24" max="24"/>
-    <col width="34" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="26" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -2690,7 +2680,6 @@
       <c r="V3" s="20" t="n"/>
       <c r="W3" s="20" t="n"/>
       <c r="X3" s="20" t="n"/>
-      <c r="Y3" s="20" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
@@ -2740,80 +2729,75 @@
       </c>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t>Prepared for BIBS?</t>
+          <t>Effort covers</t>
         </is>
       </c>
       <c r="K4" s="21" t="inlineStr">
         <is>
-          <t>Effort covers</t>
+          <t>Estimate basis</t>
         </is>
       </c>
       <c r="L4" s="21" t="inlineStr">
         <is>
-          <t>Estimate basis</t>
+          <t>Analysis &amp; design (md)</t>
         </is>
       </c>
       <c r="M4" s="21" t="inlineStr">
         <is>
-          <t>Analysis &amp; design (md)</t>
+          <t>Backend (md)</t>
         </is>
       </c>
       <c r="N4" s="21" t="inlineStr">
         <is>
-          <t>Backend (md)</t>
+          <t>Frontend (md)</t>
         </is>
       </c>
       <c r="O4" s="21" t="inlineStr">
         <is>
-          <t>Frontend (md)</t>
+          <t>Testing (md)</t>
         </is>
       </c>
       <c r="P4" s="21" t="inlineStr">
         <is>
-          <t>Testing (md)</t>
+          <t>Documentation / UAT support (md)</t>
         </is>
       </c>
       <c r="Q4" s="21" t="inlineStr">
         <is>
-          <t>Documentation / UAT support (md)</t>
+          <t>Total (md)</t>
         </is>
       </c>
       <c r="R4" s="21" t="inlineStr">
         <is>
-          <t>Total (md)</t>
+          <t>Low (-20%)</t>
         </is>
       </c>
       <c r="S4" s="21" t="inlineStr">
         <is>
-          <t>Low (-20%)</t>
+          <t>High (+20%)</t>
         </is>
       </c>
       <c r="T4" s="21" t="inlineStr">
         <is>
-          <t>High (+20%)</t>
+          <t>Cost (PHP)</t>
         </is>
       </c>
       <c r="U4" s="21" t="inlineStr">
         <is>
-          <t>Cost (PHP)</t>
+          <t>Complexity</t>
         </is>
       </c>
       <c r="V4" s="21" t="inlineStr">
         <is>
-          <t>Complexity</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="W4" s="21" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Dependencies</t>
         </is>
       </c>
       <c r="X4" s="21" t="inlineStr">
-        <is>
-          <t>Dependencies</t>
-        </is>
-      </c>
-      <c r="Y4" s="21" t="inlineStr">
         <is>
           <t>Assumptions</t>
         </is>
@@ -2867,66 +2851,61 @@
       </c>
       <c r="J5" s="12" t="inlineStr">
         <is>
-          <t>Partly: the screens prepared for BIBS use the platform components; about 8 of 35 screen files carry accessibility labels</t>
+          <t>Partial in BrokerVerse OOTB; the effort covers the missing part only: the WCAG 2.2 AA check and fixes of the module screens.</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>Partial in BrokerVerse OOTB; the effort covers the missing part only: the WCAG 2.2 AA check and fixes of the module screens.</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>Product Maintenance screens of BIBS: 35 files, about 3,800 lines.</t>
-        </is>
+          <t>Product Maintenance screens: 35 screen files, about 3,800 lines.</t>
+        </is>
+      </c>
+      <c r="L5" s="22" t="n">
+        <v>1.5</v>
       </c>
       <c r="M5" s="22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="N5" s="22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O5" s="22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P5" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q5" s="22" t="n">
         <v>1</v>
       </c>
+      <c r="Q5" s="22">
+        <f>SUM(L5:P5)</f>
+        <v/>
+      </c>
       <c r="R5" s="22">
-        <f>SUM(M5:Q5)</f>
+        <f>ROUND(Q5*(1-Assumptions!$B$6),1)</f>
         <v/>
       </c>
       <c r="S5" s="22">
-        <f>ROUND(R5*(1-Assumptions!$B$6),1)</f>
+        <f>ROUND(Q5*(1+Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="T5" s="22">
-        <f>ROUND(R5*(1+Assumptions!$B$6),1)</f>
+      <c r="T5" s="23">
+        <f>Q5*Assumptions!$B$7</f>
         <v/>
       </c>
-      <c r="U5" s="23">
-        <f>R5*Assumptions!$B$7</f>
-        <v/>
+      <c r="U5" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
       </c>
       <c r="V5" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="W5" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>BDOI's decision on the accessibility level (Annex V, PQ18)</t>
         </is>
       </c>
       <c r="X5" s="12" t="inlineStr">
-        <is>
-          <t>BDOI's decision on the accessibility level (Annex V, PQ18)</t>
-        </is>
-      </c>
-      <c r="Y5" s="12" t="inlineStr">
         <is>
           <t>Check and fixes on the 35 Product Maintenance screen files (about 3,800 lines) and the product master screens; no redesign.</t>
         </is>
@@ -2952,7 +2931,10 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
+      <c r="L6" s="22">
+        <f>SUM(L5:L5)</f>
+        <v/>
+      </c>
       <c r="M6" s="22">
         <f>SUM(M5:M5)</f>
         <v/>
@@ -2981,25 +2963,21 @@
         <f>SUM(S5:S5)</f>
         <v/>
       </c>
-      <c r="T6" s="22">
+      <c r="T6" s="23">
         <f>SUM(T5:T5)</f>
         <v/>
       </c>
-      <c r="U6" s="23">
-        <f>SUM(U5:U5)</f>
-        <v/>
-      </c>
+      <c r="U6" s="12" t="n"/>
       <c r="V6" s="12" t="n"/>
       <c r="W6" s="12" t="n"/>
       <c r="X6" s="12" t="n"/>
-      <c r="Y6" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Y6"/>
+  <autoFilter ref="A4:X6"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A2:X2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:Y506">
+  <conditionalFormatting sqref="A5:X506">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND(MOD(ROW(),2)=0,$A5&lt;&gt;"")</formula>
     </cfRule>
@@ -3008,10 +2986,10 @@
     <dataValidation sqref="E5:E506" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="BRD relation" error="Choose a value from the list (BRD relation)." type="list">
       <formula1>'Lists'!$A$2:$A$3</formula1>
     </dataValidation>
-    <dataValidation sqref="V5:V506" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
+    <dataValidation sqref="U5:U506" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Complexity" error="Choose a value from the list (Complexity)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation sqref="W5:W506" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
+    <dataValidation sqref="V5:V506" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Priority" error="Choose a value from the list (Priority)." type="list">
       <formula1>'Lists'!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -4674,7 +4652,7 @@
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>PRD-021 Not available (no committee step or hand-off). Not available in BrokerVerse OOTB. The effort is for the two BDOI texts on top of the routing already delivered for BIBS.</t>
+          <t>PRD-021 Not available (no committee step or hand-off). Not available in BrokerVerse OOTB. The effort is for the routing and the two BDOI texts.</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_CR_BRD-03_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_CR_BRD-03_Effort_Estimate_v1.0.xlsx
@@ -20,6 +20,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
+    <definedName name="Accuracy">Assumptions!$B$6</definedName>
+    <definedName name="DayRate">Assumptions!$B$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Summary'!$A$4:$B$19</definedName>
@@ -36,6 +38,8 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Best practice (blue)'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'BRD items to deliver'!$A$4:$E$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'BRD items to deliver'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Assumptions'!$A$3:$C$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Assumptions'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="10">'Lists'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -45,7 +49,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -134,6 +138,11 @@
       <color rgb="004B4B4B"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -199,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -238,7 +247,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -257,6 +272,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -991,7 +1007,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -1006,7 +1022,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1025,169 +1041,179 @@
     </row>
     <row r="2"/>
     <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+      <c r="A3" s="26" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C3" s="24" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>Hours in a man-day</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n">
+      <c r="B4" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="C4" s="25" t="inlineStr">
+      <c r="C4" s="27" t="inlineStr">
         <is>
           <t>One man-day (md) = 8 working hours</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>PHP</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t>Philippine peso</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Estimate range (plus or minus)</t>
         </is>
       </c>
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="28" t="n">
         <v>0.2</v>
       </c>
-      <c r="C6" s="25" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Each total is an estimate within plus or minus 20%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>DayRate (PHP per man-day)</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Enter the agreed day rate; the cost columns follow by formula</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="27" t="inlineStr">
         <is>
           <t>OOTB baseline</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>brokerverse-platform</t>
         </is>
       </c>
-      <c r="C8" s="25" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>iNXT BrokerVerse OOTB platform (brokerverse-platform), with the programme Feature List (column OOTB platform) as a cross-check</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="B9" s="25" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Platform size</t>
         </is>
       </c>
-      <c r="C9" s="25" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Effort from the size of the platform parts each change touches and a similar existing function; for a Partial feature, the missing part only</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Not change requests</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>BRD requirements (in scope), Integration scope and Data Migration scope items, best-practice recommendations</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Excluded</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C11" s="25" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>BDOI decisions and inputs, BDOI testing time, infrastructure</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Validity</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
-      <c r="C12" s="25" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Estimated again if the scope of a change request changes</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:C12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;8 &amp;K656565&amp;F</oddHeader>
+    <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1208,98 +1234,98 @@
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="30" t="inlineStr">
         <is>
           <t>CR Effort: BRD relation</t>
         </is>
       </c>
-      <c r="B1" s="28" t="inlineStr">
+      <c r="B1" s="30" t="inlineStr">
         <is>
           <t>CR Effort: Complexity</t>
         </is>
       </c>
-      <c r="C1" s="28" t="inlineStr">
+      <c r="C1" s="30" t="inlineStr">
         <is>
           <t>CR Effort: Priority</t>
         </is>
       </c>
-      <c r="D1" s="28" t="inlineStr">
+      <c r="D1" s="30" t="inlineStr">
         <is>
           <t>Integration &amp; DM scope: Scope</t>
         </is>
       </c>
-      <c r="E1" s="28" t="inlineStr">
+      <c r="E1" s="30" t="inlineStr">
         <is>
           <t>Best practice (blue): Suggested priority</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>Extends a BRD requirement</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="31" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="31" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="31" t="inlineStr">
         <is>
           <t>Integration scope</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="31" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>Not in any BRD</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="31" t="inlineStr">
         <is>
           <t>Data Migration scope</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="31" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="31" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
@@ -1310,7 +1336,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2370,7 +2396,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2429,7 +2455,7 @@
           <t>Points beyond the BRD available OOTB (green, no cost)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="22" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2459,7 +2485,7 @@
           <t>Man-days: Analysis &amp; design</t>
         </is>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="23">
         <f>SUM('CR Effort'!L5:L5)</f>
         <v/>
       </c>
@@ -2470,7 +2496,7 @@
           <t>Man-days: Backend</t>
         </is>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="23">
         <f>SUM('CR Effort'!M5:M5)</f>
         <v/>
       </c>
@@ -2481,7 +2507,7 @@
           <t>Man-days: Frontend</t>
         </is>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="23">
         <f>SUM('CR Effort'!N5:N5)</f>
         <v/>
       </c>
@@ -2492,7 +2518,7 @@
           <t>Man-days: Testing</t>
         </is>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="23">
         <f>SUM('CR Effort'!O5:O5)</f>
         <v/>
       </c>
@@ -2503,7 +2529,7 @@
           <t>Man-days: Documentation / UAT support</t>
         </is>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="23">
         <f>SUM('CR Effort'!P5:P5)</f>
         <v/>
       </c>
@@ -2514,7 +2540,7 @@
           <t>Total change request man-days</t>
         </is>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="23">
         <f>SUM('CR Effort'!Q5:Q5)</f>
         <v/>
       </c>
@@ -2525,7 +2551,7 @@
           <t>Range low (-20%)</t>
         </is>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="23">
         <f>SUM('CR Effort'!R5:R5)</f>
         <v/>
       </c>
@@ -2536,7 +2562,7 @@
           <t>Range high (+20%)</t>
         </is>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="23">
         <f>SUM('CR Effort'!S5:S5)</f>
         <v/>
       </c>
@@ -2547,7 +2573,7 @@
           <t>Cost in PHP at the day rate of the Assumptions sheet</t>
         </is>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="22">
         <f>SUM('CR Effort'!T5:T5)</f>
         <v/>
       </c>
@@ -2558,7 +2584,7 @@
           <t>Items covered by the Integration or Data Migration scope (no CR cost)</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="22" t="n">
         <v>23</v>
       </c>
     </row>
@@ -2578,7 +2604,7 @@
           <t>Best-practice indicative man-days (not in the CR total)</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B19" s="23" t="n">
         <v>14</v>
       </c>
     </row>
@@ -2596,7 +2622,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2859,34 +2885,34 @@
           <t>Product Maintenance screens: 35 screen files, about 3,800 lines.</t>
         </is>
       </c>
-      <c r="L5" s="22" t="n">
+      <c r="L5" s="24" t="n">
         <v>1.5</v>
       </c>
-      <c r="M5" s="22" t="n">
+      <c r="M5" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="22" t="n">
+      <c r="N5" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="O5" s="22" t="n">
+      <c r="O5" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="P5" s="22" t="n">
+      <c r="P5" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" s="22">
+      <c r="Q5" s="24">
         <f>SUM(L5:P5)</f>
         <v/>
       </c>
-      <c r="R5" s="22">
+      <c r="R5" s="24">
         <f>ROUND(Q5*(1-Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="S5" s="22">
+      <c r="S5" s="24">
         <f>ROUND(Q5*(1+Assumptions!$B$6),1)</f>
         <v/>
       </c>
-      <c r="T5" s="23">
+      <c r="T5" s="25">
         <f>Q5*Assumptions!$B$7</f>
         <v/>
       </c>
@@ -2931,39 +2957,39 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
       <c r="K6" s="12" t="n"/>
-      <c r="L6" s="22">
+      <c r="L6" s="24">
         <f>SUM(L5:L5)</f>
         <v/>
       </c>
-      <c r="M6" s="22">
+      <c r="M6" s="24">
         <f>SUM(M5:M5)</f>
         <v/>
       </c>
-      <c r="N6" s="22">
+      <c r="N6" s="24">
         <f>SUM(N5:N5)</f>
         <v/>
       </c>
-      <c r="O6" s="22">
+      <c r="O6" s="24">
         <f>SUM(O5:O5)</f>
         <v/>
       </c>
-      <c r="P6" s="22">
+      <c r="P6" s="24">
         <f>SUM(P5:P5)</f>
         <v/>
       </c>
-      <c r="Q6" s="22">
+      <c r="Q6" s="24">
         <f>SUM(Q5:Q5)</f>
         <v/>
       </c>
-      <c r="R6" s="22">
+      <c r="R6" s="24">
         <f>SUM(R5:R5)</f>
         <v/>
       </c>
-      <c r="S6" s="22">
+      <c r="S6" s="24">
         <f>SUM(S5:S5)</f>
         <v/>
       </c>
-      <c r="T6" s="23">
+      <c r="T6" s="25">
         <f>SUM(T5:T5)</f>
         <v/>
       </c>
@@ -2997,7 +3023,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3116,7 +3142,7 @@
           <t>Not in BRD</t>
         </is>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3134,7 +3160,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3253,7 +3279,7 @@
           <t>My Work: personal and team worklists</t>
         </is>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3288,7 +3314,7 @@
           <t>Reports: exports and history of produced files</t>
         </is>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3323,7 +3349,7 @@
           <t>E-mail outbox with the status of each e-mail</t>
         </is>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3358,7 +3384,7 @@
           <t>Audit trail: before and after values of every change</t>
         </is>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3376,7 +3402,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3968,7 +3994,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -4063,7 +4089,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="23" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4088,7 +4114,7 @@
           <t>High</t>
         </is>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="23" t="n">
         <v>5</v>
       </c>
     </row>
@@ -4113,7 +4139,7 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="23" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4136,7 +4162,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -4630,7 +4656,7 @@
           <t>PRD-019 Partial (no negotiation rounds or slip approval for a programme); WFL-010 Available (in-app notices). Partial in BrokerVerse OOTB: notices are available, the package slip approval is not; effort for the notice of the slip decision only.</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="23" t="n">
         <v>3.5</v>
       </c>
     </row>
@@ -4655,7 +4681,7 @@
           <t>PRD-021 Not available (no committee step or hand-off). Not available in BrokerVerse OOTB. The effort is for the routing and the two BDOI texts.</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="E23" s="23" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -4680,7 +4706,7 @@
           <t>WFL-007 Partial (deadlines and escalation for claims, complaints, leads and collections; no general turnaround engine). Partial in BrokerVerse OOTB; the planning effort covers the missing part only: the marker at a percentage of each stage's service level.</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="23" t="n">
         <v>3.5</v>
       </c>
     </row>
@@ -4698,7 +4724,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_CR_BRD-03_Effort_Estimate_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-03_Product_Maintenance/BIBS_CR_BRD-03_Effort_Estimate_v1.0.xlsx
@@ -3021,7 +3021,7 @@
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;8 &amp;K004EA8Change Request Effort Estimate&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
